--- a/VerveStacks_FRA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADD5677C-D22B-4D76-9439-FA5B805E51EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CB4EBAD-D9FD-4802-8BA2-06BA1364224B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -939,28 +939,130 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_026</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 26</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
   </si>
   <si>
     <t>distr_solelc_spv_024</t>
@@ -969,28 +1071,28 @@
     <t>connecting solar to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_solelc_spv_004</t>
@@ -1011,72 +1113,6 @@
     <t>connecting solar to buses in cluster 22</t>
   </si>
   <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_018</t>
   </si>
   <si>
@@ -1089,109 +1125,139 @@
     <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_dem2,e_gen0,e_gen2</t>
+  </si>
+  <si>
+    <t>e_dem4,e_gen0,e_gen4,e_dem0</t>
+  </si>
+  <si>
     <t>e_dem4,e_gen4</t>
   </si>
   <si>
-    <t>e_dem2,e_gen0,e_gen2</t>
-  </si>
-  <si>
-    <t>e_dem4,e_gen0,e_gen4,e_dem0</t>
+    <t>e_dem4</t>
+  </si>
+  <si>
+    <t>e_gen4,e_dem3</t>
+  </si>
+  <si>
+    <t>e_dem3</t>
+  </si>
+  <si>
+    <t>e_dem2</t>
+  </si>
+  <si>
+    <t>e_gen0,e_dem2</t>
+  </si>
+  <si>
+    <t>e_gen0,e_dem2,e_dem0</t>
+  </si>
+  <si>
+    <t>e_dem0,e_gen3</t>
+  </si>
+  <si>
+    <t>e_gen1,e_dem1</t>
+  </si>
+  <si>
+    <t>e_gen4</t>
+  </si>
+  <si>
+    <t>e_dem1,e_gen3</t>
+  </si>
+  <si>
+    <t>e_gen2,e_dem0</t>
+  </si>
+  <si>
+    <t>e_dem4,e_gen0</t>
   </si>
   <si>
     <t>e_gen4,e_gen1</t>
   </si>
   <si>
-    <t>e_gen4,e_dem3</t>
-  </si>
-  <si>
-    <t>e_dem0,e_gen3</t>
-  </si>
-  <si>
-    <t>e_gen4</t>
-  </si>
-  <si>
-    <t>e_dem1,e_gen3</t>
-  </si>
-  <si>
     <t>e_gen2</t>
   </si>
   <si>
+    <t>e_gen1,e_gen3,e_dem1</t>
+  </si>
+  <si>
+    <t>e_dem0,e_gen2</t>
+  </si>
+  <si>
     <t>e_dem0,e_gen4,e_gen1</t>
   </si>
   <si>
-    <t>e_dem0,e_gen2</t>
-  </si>
-  <si>
-    <t>e_dem4</t>
-  </si>
-  <si>
-    <t>e_dem3</t>
-  </si>
-  <si>
-    <t>e_gen2,e_dem0</t>
-  </si>
-  <si>
-    <t>e_gen1,e_dem1</t>
-  </si>
-  <si>
-    <t>e_dem2</t>
-  </si>
-  <si>
-    <t>e_gen1,e_gen3,e_dem1</t>
-  </si>
-  <si>
-    <t>e_dem4,e_gen0</t>
-  </si>
-  <si>
     <t>e_dem3,e_gen1</t>
   </si>
   <si>
-    <t>e_gen0,e_dem2</t>
-  </si>
-  <si>
-    <t>e_gen0,e_dem2,e_dem0</t>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
   </si>
   <si>
     <t>distr_wonelc_won_010</t>
@@ -1206,10 +1272,10 @@
     <t>connecting wind onshore to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
   </si>
   <si>
     <t>distr_wonelc_won_016</t>
@@ -1242,52 +1308,16 @@
     <t>connecting wind onshore to buses in cluster 22</t>
   </si>
   <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
     <t>distr_wonelc_won_018</t>
@@ -1332,34 +1362,46 @@
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_gen3,e_dem1</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_gen1</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_dem1</t>
   </si>
   <si>
     <t>elc_won_010</t>
@@ -1368,7 +1410,7 @@
     <t>elc_won_011</t>
   </si>
   <si>
-    <t>elc_won_001</t>
+    <t>elc_won_028</t>
   </si>
   <si>
     <t>elc_won_016</t>
@@ -1395,37 +1437,13 @@
     <t>elc_won_022</t>
   </si>
   <si>
-    <t>e_dem1</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_gen3,e_dem1</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_gen1</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_dem2,e_gen2</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
   </si>
   <si>
     <t>elc_won_018</t>
@@ -1455,22 +1473,46 @@
     <t>elc_won_003</t>
   </si>
   <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_dem2,e_gen2</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wofelc_wof_017</t>
@@ -1491,6 +1533,30 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_010</t>
   </si>
   <si>
@@ -1503,76 +1569,34 @@
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_004</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_gen0,e_dem2,e_dem4</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
   </si>
   <si>
     <t>elc_wof_017</t>
@@ -1584,49 +1608,25 @@
     <t>elc_wof_006</t>
   </si>
   <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
     <t>elc_wof_010</t>
   </si>
   <si>
     <t>elc_wof_001</t>
   </si>
   <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
     <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_gen0,e_dem2,e_dem4</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -6675,7 +6675,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{234DE926-6C64-4950-99A9-C2DBEB1CDE8D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E02236E-7B3E-4AB7-B67F-AF41B09F8BBF}">
   <dimension ref="B9:BD40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6913,16 +6913,16 @@
         <v>270</v>
       </c>
       <c r="Y11" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="Z11" t="s">
         <v>334</v>
       </c>
       <c r="AA11">
-        <v>0.99306659504794947</v>
+        <v>0.99074898552043367</v>
       </c>
       <c r="AB11">
-        <v>127.11242412092568</v>
+        <v>169.6019321253824</v>
       </c>
       <c r="AD11" t="s">
         <v>269</v>
@@ -6952,13 +6952,13 @@
         <v>411</v>
       </c>
       <c r="AN11" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="AO11">
-        <v>0.99266379654332038</v>
+        <v>0.98974092979483974</v>
       </c>
       <c r="AP11">
-        <v>134.49706337246005</v>
+        <v>188.08295376127217</v>
       </c>
       <c r="AR11" t="s">
         <v>269</v>
@@ -6988,13 +6988,13 @@
         <v>482</v>
       </c>
       <c r="BB11" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="BC11">
-        <v>0.96193435381293269</v>
+        <v>0.98987270103949943</v>
       </c>
       <c r="BD11">
-        <v>697.87018009623353</v>
+        <v>185.6671476091779</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7059,16 +7059,16 @@
         <v>274</v>
       </c>
       <c r="Y12" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="Z12" t="s">
         <v>335</v>
       </c>
       <c r="AA12">
-        <v>0.99074898552043367</v>
+        <v>0.98871903666488603</v>
       </c>
       <c r="AB12">
-        <v>169.6019321253824</v>
+        <v>206.81766114375711</v>
       </c>
       <c r="AD12" t="s">
         <v>269</v>
@@ -7098,13 +7098,13 @@
         <v>412</v>
       </c>
       <c r="AN12" t="s">
-        <v>345</v>
+        <v>413</v>
       </c>
       <c r="AO12">
-        <v>0.99373126046519367</v>
+        <v>0.99454803063103558</v>
       </c>
       <c r="AP12">
-        <v>114.92689147144912</v>
+        <v>99.952771764347304</v>
       </c>
       <c r="AR12" t="s">
         <v>269</v>
@@ -7134,13 +7134,13 @@
         <v>483</v>
       </c>
       <c r="BB12" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="BC12">
-        <v>0.97296139770869694</v>
+        <v>0.98127791933809161</v>
       </c>
       <c r="BD12">
-        <v>495.70770867388939</v>
+        <v>343.23814546832108</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7205,16 +7205,16 @@
         <v>276</v>
       </c>
       <c r="Y13" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Z13" t="s">
         <v>336</v>
       </c>
       <c r="AA13">
-        <v>0.98871903666488603</v>
+        <v>0.99306659504794947</v>
       </c>
       <c r="AB13">
-        <v>206.81766114375711</v>
+        <v>127.11242412092568</v>
       </c>
       <c r="AD13" t="s">
         <v>269</v>
@@ -7241,16 +7241,16 @@
         <v>359</v>
       </c>
       <c r="AM13" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN13" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="AO13">
-        <v>0.9782800434603014</v>
+        <v>0.99668790123920514</v>
       </c>
       <c r="AP13">
-        <v>398.19920322780678</v>
+        <v>60.721810614572206</v>
       </c>
       <c r="AR13" t="s">
         <v>269</v>
@@ -7280,13 +7280,13 @@
         <v>484</v>
       </c>
       <c r="BB13" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="BC13">
-        <v>0.97519287309306191</v>
+        <v>0.97024476000465243</v>
       </c>
       <c r="BD13">
-        <v>454.79732662719823</v>
+        <v>545.51273324803913</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7351,16 +7351,16 @@
         <v>278</v>
       </c>
       <c r="Y14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z14" t="s">
         <v>337</v>
       </c>
       <c r="AA14">
-        <v>0.99036558192019719</v>
+        <v>0.98943698292665661</v>
       </c>
       <c r="AB14">
-        <v>176.63099812971814</v>
+        <v>193.6553130112959</v>
       </c>
       <c r="AD14" t="s">
         <v>269</v>
@@ -7387,16 +7387,16 @@
         <v>361</v>
       </c>
       <c r="AM14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN14" t="s">
-        <v>415</v>
+        <v>339</v>
       </c>
       <c r="AO14">
-        <v>0.99265977528547111</v>
+        <v>0.99396981584832544</v>
       </c>
       <c r="AP14">
-        <v>134.57078643303035</v>
+        <v>110.55337611403426</v>
       </c>
       <c r="AR14" t="s">
         <v>269</v>
@@ -7426,13 +7426,13 @@
         <v>485</v>
       </c>
       <c r="BB14" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="BC14">
-        <v>0.9861533465577601</v>
+        <v>0.98470059323114356</v>
       </c>
       <c r="BD14">
-        <v>253.85531310773223</v>
+        <v>280.48912409570232</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7497,16 +7497,16 @@
         <v>280</v>
       </c>
       <c r="Y15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Z15" t="s">
         <v>338</v>
       </c>
       <c r="AA15">
-        <v>0.99380321394043492</v>
+        <v>0.98844033553992972</v>
       </c>
       <c r="AB15">
-        <v>113.60774442536065</v>
+        <v>211.92718176795447</v>
       </c>
       <c r="AD15" t="s">
         <v>269</v>
@@ -7536,13 +7536,13 @@
         <v>416</v>
       </c>
       <c r="AN15" t="s">
-        <v>417</v>
+        <v>354</v>
       </c>
       <c r="AO15">
-        <v>0.99102919755488506</v>
+        <v>0.99536525245638341</v>
       </c>
       <c r="AP15">
-        <v>164.46471149377308</v>
+        <v>84.970371632971023</v>
       </c>
       <c r="AR15" t="s">
         <v>269</v>
@@ -7572,13 +7572,13 @@
         <v>486</v>
       </c>
       <c r="BB15" t="s">
-        <v>338</v>
+        <v>487</v>
       </c>
       <c r="BC15">
-        <v>0.98810453029075374</v>
+        <v>0.98449716664191456</v>
       </c>
       <c r="BD15">
-        <v>218.08361133618146</v>
+        <v>284.21861156490036</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7643,16 +7643,16 @@
         <v>282</v>
       </c>
       <c r="Y16" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Z16" t="s">
         <v>339</v>
       </c>
       <c r="AA16">
-        <v>0.98950922221532345</v>
+        <v>0.97057104063486466</v>
       </c>
       <c r="AB16">
-        <v>192.33092605240353</v>
+        <v>539.53092169414879</v>
       </c>
       <c r="AD16" t="s">
         <v>269</v>
@@ -7679,16 +7679,16 @@
         <v>365</v>
       </c>
       <c r="AM16" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AN16" t="s">
-        <v>419</v>
+        <v>345</v>
       </c>
       <c r="AO16">
-        <v>0.98980925931588959</v>
+        <v>0.99568755601261638</v>
       </c>
       <c r="AP16">
-        <v>186.83024587535752</v>
+        <v>79.061473102033588</v>
       </c>
       <c r="AR16" t="s">
         <v>269</v>
@@ -7715,16 +7715,16 @@
         <v>458</v>
       </c>
       <c r="BA16" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="BB16" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="BC16">
-        <v>0.98987270103949943</v>
+        <v>0.96620291469621566</v>
       </c>
       <c r="BD16">
-        <v>185.6671476091779</v>
+        <v>619.61323056937977</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7789,16 +7789,16 @@
         <v>284</v>
       </c>
       <c r="Y17" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="Z17" t="s">
         <v>340</v>
       </c>
       <c r="AA17">
-        <v>0.99058732692867291</v>
+        <v>0.99133738566043939</v>
       </c>
       <c r="AB17">
-        <v>172.56567297432909</v>
+        <v>158.81459622527697</v>
       </c>
       <c r="AD17" t="s">
         <v>269</v>
@@ -7825,16 +7825,16 @@
         <v>367</v>
       </c>
       <c r="AM17" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AN17" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AO17">
-        <v>0.99194279509442385</v>
+        <v>0.99099144211961365</v>
       </c>
       <c r="AP17">
-        <v>147.71542326889627</v>
+        <v>165.1568944737499</v>
       </c>
       <c r="AR17" t="s">
         <v>269</v>
@@ -7861,16 +7861,16 @@
         <v>460</v>
       </c>
       <c r="BA17" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="BB17" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="BC17">
-        <v>0.97260423035674359</v>
+        <v>0.96972263277531634</v>
       </c>
       <c r="BD17">
-        <v>502.2557767930341</v>
+        <v>555.08506578586628</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7935,16 +7935,16 @@
         <v>286</v>
       </c>
       <c r="Y18" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="Z18" t="s">
         <v>341</v>
       </c>
       <c r="AA18">
-        <v>0.99456953758198319</v>
+        <v>0.99560473871467581</v>
       </c>
       <c r="AB18">
-        <v>99.558477663641582</v>
+        <v>80.579790230943289</v>
       </c>
       <c r="AD18" t="s">
         <v>269</v>
@@ -7971,16 +7971,16 @@
         <v>369</v>
       </c>
       <c r="AM18" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AN18" t="s">
-        <v>422</v>
+        <v>354</v>
       </c>
       <c r="AO18">
-        <v>0.9947696749839372</v>
+        <v>0.99702764180837389</v>
       </c>
       <c r="AP18">
-        <v>95.889291961151685</v>
+        <v>54.493233513145114</v>
       </c>
       <c r="AR18" t="s">
         <v>269</v>
@@ -8007,16 +8007,16 @@
         <v>462</v>
       </c>
       <c r="BA18" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="BB18" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="BC18">
-        <v>0.98578667690837229</v>
+        <v>0.96193435381293269</v>
       </c>
       <c r="BD18">
-        <v>260.57759001317498</v>
+        <v>697.87018009623353</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8081,16 +8081,16 @@
         <v>288</v>
       </c>
       <c r="Y19" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Z19" t="s">
         <v>342</v>
       </c>
       <c r="AA19">
-        <v>0.99455764054307205</v>
+        <v>0.99188284926968906</v>
       </c>
       <c r="AB19">
-        <v>99.77659004367905</v>
+        <v>148.81443005569966</v>
       </c>
       <c r="AD19" t="s">
         <v>269</v>
@@ -8117,16 +8117,16 @@
         <v>371</v>
       </c>
       <c r="AM19" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="AN19" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AO19">
-        <v>0.99568755601261638</v>
+        <v>0.9782800434603014</v>
       </c>
       <c r="AP19">
-        <v>79.061473102033588</v>
+        <v>398.19920322780678</v>
       </c>
       <c r="AR19" t="s">
         <v>269</v>
@@ -8153,16 +8153,16 @@
         <v>464</v>
       </c>
       <c r="BA19" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="BB19" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="BC19">
-        <v>0.98470059323114356</v>
+        <v>0.97296139770869694</v>
       </c>
       <c r="BD19">
-        <v>280.48912409570232</v>
+        <v>495.70770867388939</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8227,16 +8227,16 @@
         <v>290</v>
       </c>
       <c r="Y20" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="Z20" t="s">
         <v>337</v>
       </c>
       <c r="AA20">
-        <v>0.99510234843435064</v>
+        <v>0.99628107477919792</v>
       </c>
       <c r="AB20">
-        <v>89.790278703571531</v>
+        <v>68.180295714705792</v>
       </c>
       <c r="AD20" t="s">
         <v>269</v>
@@ -8263,16 +8263,16 @@
         <v>373</v>
       </c>
       <c r="AM20" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AN20" t="s">
-        <v>339</v>
+        <v>422</v>
       </c>
       <c r="AO20">
-        <v>0.99099144211961365</v>
+        <v>0.99299955705033549</v>
       </c>
       <c r="AP20">
-        <v>165.1568944737499</v>
+        <v>128.34145407718299</v>
       </c>
       <c r="AR20" t="s">
         <v>269</v>
@@ -8299,16 +8299,16 @@
         <v>466</v>
       </c>
       <c r="BA20" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="BB20" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="BC20">
-        <v>0.97024476000465243</v>
+        <v>0.97519287309306191</v>
       </c>
       <c r="BD20">
-        <v>545.51273324803913</v>
+        <v>454.79732662719823</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8373,16 +8373,16 @@
         <v>292</v>
       </c>
       <c r="Y21" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="Z21" t="s">
         <v>343</v>
       </c>
       <c r="AA21">
-        <v>0.98506785527064555</v>
+        <v>0.9922832499015094</v>
       </c>
       <c r="AB21">
-        <v>273.75598670483231</v>
+        <v>141.47375180566112</v>
       </c>
       <c r="AD21" t="s">
         <v>269</v>
@@ -8409,16 +8409,16 @@
         <v>375</v>
       </c>
       <c r="AM21" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AN21" t="s">
-        <v>352</v>
+        <v>424</v>
       </c>
       <c r="AO21">
-        <v>0.99702764180837389</v>
+        <v>0.98967297418060196</v>
       </c>
       <c r="AP21">
-        <v>54.493233513145114</v>
+        <v>189.3288066889647</v>
       </c>
       <c r="AR21" t="s">
         <v>269</v>
@@ -8445,16 +8445,16 @@
         <v>468</v>
       </c>
       <c r="BA21" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="BB21" t="s">
-        <v>446</v>
+        <v>340</v>
       </c>
       <c r="BC21">
-        <v>0.98430504414907682</v>
+        <v>0.97260423035674359</v>
       </c>
       <c r="BD21">
-        <v>287.74085726692596</v>
+        <v>502.2557767930341</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8519,16 +8519,16 @@
         <v>294</v>
       </c>
       <c r="Y22" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="Z22" t="s">
         <v>344</v>
       </c>
       <c r="AA22">
-        <v>0.99592139175292038</v>
+        <v>0.99427514814587914</v>
       </c>
       <c r="AB22">
-        <v>74.774484529793384</v>
+        <v>104.95561732554863</v>
       </c>
       <c r="AD22" t="s">
         <v>269</v>
@@ -8555,16 +8555,16 @@
         <v>377</v>
       </c>
       <c r="AM22" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AN22" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AO22">
-        <v>0.99102447886015177</v>
+        <v>0.99266379654332038</v>
       </c>
       <c r="AP22">
-        <v>164.55122089721749</v>
+        <v>134.49706337246005</v>
       </c>
       <c r="AR22" t="s">
         <v>269</v>
@@ -8591,16 +8591,16 @@
         <v>470</v>
       </c>
       <c r="BA22" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="BB22" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="BC22">
-        <v>0.99428710319679992</v>
+        <v>0.98578667690837229</v>
       </c>
       <c r="BD22">
-        <v>104.7364413920006</v>
+        <v>260.57759001317498</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8665,16 +8665,16 @@
         <v>296</v>
       </c>
       <c r="Y23" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="Z23" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="AA23">
-        <v>0.98943698292665661</v>
+        <v>0.99380321394043492</v>
       </c>
       <c r="AB23">
-        <v>193.6553130112959</v>
+        <v>113.60774442536065</v>
       </c>
       <c r="AD23" t="s">
         <v>269</v>
@@ -8701,16 +8701,16 @@
         <v>379</v>
       </c>
       <c r="AM23" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AN23" t="s">
         <v>337</v>
       </c>
       <c r="AO23">
-        <v>0.98974092979483974</v>
+        <v>0.99373126046519367</v>
       </c>
       <c r="AP23">
-        <v>188.08295376127217</v>
+        <v>114.92689147144912</v>
       </c>
       <c r="AR23" t="s">
         <v>269</v>
@@ -8737,16 +8737,16 @@
         <v>472</v>
       </c>
       <c r="BA23" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="BB23" t="s">
-        <v>349</v>
+        <v>437</v>
       </c>
       <c r="BC23">
-        <v>0.98127791933809161</v>
+        <v>0.98430504414907682</v>
       </c>
       <c r="BD23">
-        <v>343.23814546832108</v>
+        <v>287.74085726692596</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8811,16 +8811,16 @@
         <v>298</v>
       </c>
       <c r="Y24" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="Z24" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="AA24">
-        <v>0.98844033553992972</v>
+        <v>0.98950922221532345</v>
       </c>
       <c r="AB24">
-        <v>211.92718176795447</v>
+        <v>192.33092605240353</v>
       </c>
       <c r="AD24" t="s">
         <v>269</v>
@@ -8847,16 +8847,16 @@
         <v>381</v>
       </c>
       <c r="AM24" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AN24" t="s">
-        <v>429</v>
+        <v>336</v>
       </c>
       <c r="AO24">
-        <v>0.99454803063103558</v>
+        <v>0.99102447886015177</v>
       </c>
       <c r="AP24">
-        <v>99.952771764347304</v>
+        <v>164.55122089721749</v>
       </c>
       <c r="AR24" t="s">
         <v>269</v>
@@ -8883,16 +8883,16 @@
         <v>474</v>
       </c>
       <c r="BA24" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="BB24" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="BC24">
-        <v>0.98116881440348735</v>
+        <v>0.99428710319679992</v>
       </c>
       <c r="BD24">
-        <v>345.23840260273118</v>
+        <v>104.7364413920006</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8957,16 +8957,16 @@
         <v>300</v>
       </c>
       <c r="Y25" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="Z25" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA25">
-        <v>0.97057104063486466</v>
+        <v>0.99058732692867291</v>
       </c>
       <c r="AB25">
-        <v>539.53092169414879</v>
+        <v>172.56567297432909</v>
       </c>
       <c r="AD25" t="s">
         <v>269</v>
@@ -8993,16 +8993,16 @@
         <v>383</v>
       </c>
       <c r="AM25" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AN25" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AO25">
-        <v>0.99299955705033549</v>
+        <v>0.99265977528547111</v>
       </c>
       <c r="AP25">
-        <v>128.34145407718299</v>
+        <v>134.57078643303035</v>
       </c>
       <c r="AR25" t="s">
         <v>269</v>
@@ -9029,16 +9029,16 @@
         <v>476</v>
       </c>
       <c r="BA25" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="BB25" t="s">
-        <v>497</v>
+        <v>337</v>
       </c>
       <c r="BC25">
-        <v>0.98449716664191456</v>
+        <v>0.9861533465577601</v>
       </c>
       <c r="BD25">
-        <v>284.21861156490036</v>
+        <v>253.85531310773223</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9103,16 +9103,16 @@
         <v>302</v>
       </c>
       <c r="Y26" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="Z26" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AA26">
-        <v>0.99203796026218938</v>
+        <v>0.99456953758198319</v>
       </c>
       <c r="AB26">
-        <v>145.97072852652775</v>
+        <v>99.558477663641582</v>
       </c>
       <c r="AD26" t="s">
         <v>269</v>
@@ -9139,16 +9139,16 @@
         <v>385</v>
       </c>
       <c r="AM26" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AN26" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="AO26">
-        <v>0.98967297418060196</v>
+        <v>0.99102919755488506</v>
       </c>
       <c r="AP26">
-        <v>189.3288066889647</v>
+        <v>164.46471149377308</v>
       </c>
       <c r="AR26" t="s">
         <v>269</v>
@@ -9178,13 +9178,13 @@
         <v>498</v>
       </c>
       <c r="BB26" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="BC26">
-        <v>0.96620291469621566</v>
+        <v>0.98810453029075374</v>
       </c>
       <c r="BD26">
-        <v>619.61323056937977</v>
+        <v>218.08361133618146</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9252,7 +9252,7 @@
         <v>251</v>
       </c>
       <c r="Z27" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AA27">
         <v>0.99361327661798182</v>
@@ -9285,16 +9285,16 @@
         <v>387</v>
       </c>
       <c r="AM27" t="s">
+        <v>432</v>
+      </c>
+      <c r="AN27" t="s">
         <v>433</v>
       </c>
-      <c r="AN27" t="s">
-        <v>434</v>
-      </c>
       <c r="AO27">
-        <v>0.99296607263934833</v>
+        <v>0.98980925931588959</v>
       </c>
       <c r="AP27">
-        <v>128.95533494527976</v>
+        <v>186.83024587535752</v>
       </c>
       <c r="AR27" t="s">
         <v>269</v>
@@ -9324,13 +9324,13 @@
         <v>499</v>
       </c>
       <c r="BB27" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="BC27">
-        <v>0.96972263277531634</v>
+        <v>0.98116881440348735</v>
       </c>
       <c r="BD27">
-        <v>555.08506578586628</v>
+        <v>345.23840260273118</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9398,7 +9398,7 @@
         <v>256</v>
       </c>
       <c r="Z28" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="AA28">
         <v>0.99105162171633221</v>
@@ -9431,16 +9431,16 @@
         <v>389</v>
       </c>
       <c r="AM28" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AN28" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="AO28">
-        <v>0.98992222971133592</v>
+        <v>0.99194279509442385</v>
       </c>
       <c r="AP28">
-        <v>184.75912195884121</v>
+        <v>147.71542326889627</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9505,16 +9505,16 @@
         <v>308</v>
       </c>
       <c r="Y29" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="Z29" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AA29">
-        <v>0.98066337855689323</v>
+        <v>0.99203796026218938</v>
       </c>
       <c r="AB29">
-        <v>354.5047264569576</v>
+        <v>145.97072852652775</v>
       </c>
       <c r="AD29" t="s">
         <v>269</v>
@@ -9541,16 +9541,16 @@
         <v>391</v>
       </c>
       <c r="AM29" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AN29" t="s">
-        <v>338</v>
+        <v>424</v>
       </c>
       <c r="AO29">
-        <v>0.99027568948244393</v>
+        <v>0.9947696749839372</v>
       </c>
       <c r="AP29">
-        <v>178.27902615519463</v>
+        <v>95.889291961151685</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9615,16 +9615,16 @@
         <v>310</v>
       </c>
       <c r="Y30" t="s">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="Z30" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="AA30">
-        <v>0.99010316852626312</v>
+        <v>0.99132345360703722</v>
       </c>
       <c r="AB30">
-        <v>181.44191035184215</v>
+        <v>159.07001720431779</v>
       </c>
       <c r="AD30" t="s">
         <v>269</v>
@@ -9651,16 +9651,16 @@
         <v>393</v>
       </c>
       <c r="AM30" t="s">
+        <v>436</v>
+      </c>
+      <c r="AN30" t="s">
         <v>437</v>
       </c>
-      <c r="AN30" t="s">
-        <v>438</v>
-      </c>
       <c r="AO30">
-        <v>0.98523670671496333</v>
+        <v>0.98552281783188733</v>
       </c>
       <c r="AP30">
-        <v>270.66037689233832</v>
+        <v>265.41500641539994</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9725,16 +9725,16 @@
         <v>312</v>
       </c>
       <c r="Y31" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Z31" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AA31">
-        <v>0.98887858934711803</v>
+        <v>0.99036558192019719</v>
       </c>
       <c r="AB31">
-        <v>203.89252863617014</v>
+        <v>176.63099812971814</v>
       </c>
       <c r="AD31" t="s">
         <v>269</v>
@@ -9761,16 +9761,16 @@
         <v>395</v>
       </c>
       <c r="AM31" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AN31" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="AO31">
-        <v>0.99104096459785573</v>
+        <v>0.98584846679356541</v>
       </c>
       <c r="AP31">
-        <v>164.24898237264404</v>
+        <v>259.44477545130104</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9835,16 +9835,16 @@
         <v>314</v>
       </c>
       <c r="Y32" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="Z32" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="AA32">
-        <v>0.99132345360703722</v>
+        <v>0.98066337855689323</v>
       </c>
       <c r="AB32">
-        <v>159.07001720431779</v>
+        <v>354.5047264569576</v>
       </c>
       <c r="AD32" t="s">
         <v>269</v>
@@ -9871,16 +9871,16 @@
         <v>397</v>
       </c>
       <c r="AM32" t="s">
+        <v>439</v>
+      </c>
+      <c r="AN32" t="s">
         <v>440</v>
       </c>
-      <c r="AN32" t="s">
-        <v>422</v>
-      </c>
       <c r="AO32">
-        <v>0.99260627833960313</v>
+        <v>0.99296607263934833</v>
       </c>
       <c r="AP32">
-        <v>135.55156377394354</v>
+        <v>128.95533494527976</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9945,16 +9945,16 @@
         <v>316</v>
       </c>
       <c r="Y33" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="Z33" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AA33">
-        <v>0.99082744703600512</v>
+        <v>0.99010316852626312</v>
       </c>
       <c r="AB33">
-        <v>168.16347100657356</v>
+        <v>181.44191035184215</v>
       </c>
       <c r="AD33" t="s">
         <v>269</v>
@@ -9984,13 +9984,13 @@
         <v>441</v>
       </c>
       <c r="AN33" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="AO33">
-        <v>0.98220670102649277</v>
+        <v>0.98992222971133592</v>
       </c>
       <c r="AP33">
-        <v>326.21048118096536</v>
+        <v>184.75912195884121</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -10055,16 +10055,16 @@
         <v>318</v>
       </c>
       <c r="Y34" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="Z34" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AA34">
-        <v>0.99238998569866288</v>
+        <v>0.98887858934711803</v>
       </c>
       <c r="AB34">
-        <v>139.51692885784635</v>
+        <v>203.89252863617014</v>
       </c>
       <c r="AD34" t="s">
         <v>269</v>
@@ -10094,13 +10094,13 @@
         <v>442</v>
       </c>
       <c r="AN34" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="AO34">
-        <v>0.99536525245638341</v>
+        <v>0.99027568948244393</v>
       </c>
       <c r="AP34">
-        <v>84.970371632971023</v>
+        <v>178.27902615519463</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -10165,16 +10165,16 @@
         <v>320</v>
       </c>
       <c r="Y35" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="Z35" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AA35">
-        <v>0.99133738566043939</v>
+        <v>0.99592139175292038</v>
       </c>
       <c r="AB35">
-        <v>158.81459622527697</v>
+        <v>74.774484529793384</v>
       </c>
       <c r="AD35" t="s">
         <v>269</v>
@@ -10204,13 +10204,13 @@
         <v>443</v>
       </c>
       <c r="AN35" t="s">
-        <v>334</v>
+        <v>444</v>
       </c>
       <c r="AO35">
-        <v>0.99668790123920514</v>
+        <v>0.98523670671496333</v>
       </c>
       <c r="AP35">
-        <v>60.721810614572206</v>
+        <v>270.66037689233832</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -10275,16 +10275,16 @@
         <v>322</v>
       </c>
       <c r="Y36" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Z36" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AA36">
-        <v>0.99560473871467581</v>
+        <v>0.99455764054307205</v>
       </c>
       <c r="AB36">
-        <v>80.579790230943289</v>
+        <v>99.77659004367905</v>
       </c>
       <c r="AD36" t="s">
         <v>269</v>
@@ -10311,16 +10311,16 @@
         <v>405</v>
       </c>
       <c r="AM36" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AN36" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="AO36">
-        <v>0.99396981584832544</v>
+        <v>0.99104096459785573</v>
       </c>
       <c r="AP36">
-        <v>110.55337611403426</v>
+        <v>164.24898237264404</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -10385,16 +10385,16 @@
         <v>324</v>
       </c>
       <c r="Y37" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="Z37" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="AA37">
-        <v>0.99188284926968906</v>
+        <v>0.99510234843435064</v>
       </c>
       <c r="AB37">
-        <v>148.81443005569966</v>
+        <v>89.790278703571531</v>
       </c>
       <c r="AD37" t="s">
         <v>269</v>
@@ -10421,16 +10421,16 @@
         <v>407</v>
       </c>
       <c r="AM37" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN37" t="s">
-        <v>446</v>
+        <v>424</v>
       </c>
       <c r="AO37">
-        <v>0.98552281783188733</v>
+        <v>0.99260627833960313</v>
       </c>
       <c r="AP37">
-        <v>265.41500641539994</v>
+        <v>135.55156377394354</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10495,16 +10495,16 @@
         <v>326</v>
       </c>
       <c r="Y38" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="Z38" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="AA38">
-        <v>0.99628107477919792</v>
+        <v>0.98506785527064555</v>
       </c>
       <c r="AB38">
-        <v>68.180295714705792</v>
+        <v>273.75598670483231</v>
       </c>
       <c r="AD38" t="s">
         <v>269</v>
@@ -10534,13 +10534,13 @@
         <v>447</v>
       </c>
       <c r="AN38" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="AO38">
-        <v>0.98584846679356541</v>
+        <v>0.98220670102649277</v>
       </c>
       <c r="AP38">
-        <v>259.44477545130104</v>
+        <v>326.21048118096536</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -10605,16 +10605,16 @@
         <v>328</v>
       </c>
       <c r="Y39" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="Z39" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="AA39">
-        <v>0.9922832499015094</v>
+        <v>0.99082744703600512</v>
       </c>
       <c r="AB39">
-        <v>141.47375180566112</v>
+        <v>168.16347100657356</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -10679,16 +10679,16 @@
         <v>330</v>
       </c>
       <c r="Y40" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="Z40" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AA40">
-        <v>0.99427514814587914</v>
+        <v>0.99238998569866288</v>
       </c>
       <c r="AB40">
-        <v>104.95561732554863</v>
+        <v>139.51692885784635</v>
       </c>
     </row>
   </sheetData>
@@ -10697,7 +10697,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0318E5B9-9990-425A-A4B5-C0C025D98C2A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C9E5246-6D5D-4A7F-8DA7-87655161E1F4}">
   <dimension ref="B9:Z38"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10809,7 +10809,7 @@
         <v>500</v>
       </c>
       <c r="K11" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="L11">
         <v>7.5384385218371168</v>
@@ -10842,7 +10842,7 @@
         <v>556</v>
       </c>
       <c r="X11" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="Y11">
         <v>38.411999999999999</v>
@@ -10877,7 +10877,7 @@
         <v>502</v>
       </c>
       <c r="K12" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="L12">
         <v>8.5464211426904182</v>
@@ -10910,7 +10910,7 @@
         <v>558</v>
       </c>
       <c r="X12" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="Y12">
         <v>9.3112499999999994</v>
@@ -10945,7 +10945,7 @@
         <v>504</v>
       </c>
       <c r="K13" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="L13">
         <v>1.5340845206129941</v>
@@ -10978,7 +10978,7 @@
         <v>560</v>
       </c>
       <c r="X13" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="Y13">
         <v>9.5287500000000005</v>
@@ -11013,7 +11013,7 @@
         <v>506</v>
       </c>
       <c r="K14" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="L14">
         <v>17.766367792804527</v>
@@ -11046,7 +11046,7 @@
         <v>562</v>
       </c>
       <c r="X14" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="Y14">
         <v>2.1749999999999999E-2</v>
@@ -11081,7 +11081,7 @@
         <v>508</v>
       </c>
       <c r="K15" t="s">
-        <v>444</v>
+        <v>415</v>
       </c>
       <c r="L15">
         <v>3.7020770759557711</v>
@@ -11114,7 +11114,7 @@
         <v>564</v>
       </c>
       <c r="X15" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="Y15">
         <v>8.2590000000000003</v>
@@ -11149,7 +11149,7 @@
         <v>510</v>
       </c>
       <c r="K16" t="s">
-        <v>442</v>
+        <v>416</v>
       </c>
       <c r="L16">
         <v>28.612118601835597</v>
@@ -11182,7 +11182,7 @@
         <v>566</v>
       </c>
       <c r="X16" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="Y16">
         <v>0.40575</v>
@@ -11217,7 +11217,7 @@
         <v>512</v>
       </c>
       <c r="K17" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="L17">
         <v>54.523871060763341</v>
@@ -11250,7 +11250,7 @@
         <v>568</v>
       </c>
       <c r="X17" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="Y17">
         <v>6.4290000000000003</v>
@@ -11285,7 +11285,7 @@
         <v>514</v>
       </c>
       <c r="K18" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="L18">
         <v>21.752928174024966</v>
@@ -11318,7 +11318,7 @@
         <v>570</v>
       </c>
       <c r="X18" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="Y18">
         <v>0.10199999999999999</v>
@@ -11353,7 +11353,7 @@
         <v>516</v>
       </c>
       <c r="K19" t="s">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="L19">
         <v>75.839981284454382</v>
@@ -11386,7 +11386,7 @@
         <v>572</v>
       </c>
       <c r="X19" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="Y19">
         <v>27.910499999999999</v>
@@ -11421,7 +11421,7 @@
         <v>518</v>
       </c>
       <c r="K20" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="L20">
         <v>15.373849239963436</v>
@@ -11454,7 +11454,7 @@
         <v>574</v>
       </c>
       <c r="X20" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="Y20">
         <v>2.7322500000000001</v>
@@ -11489,7 +11489,7 @@
         <v>520</v>
       </c>
       <c r="K21" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="L21">
         <v>20.941488433116</v>
@@ -11522,7 +11522,7 @@
         <v>576</v>
       </c>
       <c r="X21" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="Y21">
         <v>69.386250000000004</v>
@@ -11557,7 +11557,7 @@
         <v>522</v>
       </c>
       <c r="K22" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="L22">
         <v>10.348692721070078</v>
@@ -11590,7 +11590,7 @@
         <v>578</v>
       </c>
       <c r="X22" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="Y22">
         <v>80.700749999999999</v>
@@ -11625,7 +11625,7 @@
         <v>524</v>
       </c>
       <c r="K23" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="L23">
         <v>30.807418987588004</v>
@@ -11658,7 +11658,7 @@
         <v>580</v>
       </c>
       <c r="X23" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="Y23">
         <v>19.849499999999999</v>
@@ -11693,7 +11693,7 @@
         <v>526</v>
       </c>
       <c r="K24" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="L24">
         <v>6.8734480919946561</v>
@@ -11726,7 +11726,7 @@
         <v>582</v>
       </c>
       <c r="X24" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="Y24">
         <v>35.221499999999999</v>
@@ -11761,7 +11761,7 @@
         <v>528</v>
       </c>
       <c r="K25" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="L25">
         <v>45.970542554915504</v>
@@ -11794,7 +11794,7 @@
         <v>584</v>
       </c>
       <c r="X25" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="Y25">
         <v>88.549499999999995</v>
@@ -11829,7 +11829,7 @@
         <v>530</v>
       </c>
       <c r="K26" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="L26">
         <v>102.16105468063856</v>
@@ -11862,7 +11862,7 @@
         <v>586</v>
       </c>
       <c r="X26" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="Y26">
         <v>42.073500000000003</v>
@@ -11897,7 +11897,7 @@
         <v>532</v>
       </c>
       <c r="K27" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="L27">
         <v>33.663807794729088</v>
@@ -11930,7 +11930,7 @@
         <v>588</v>
       </c>
       <c r="X27" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="Y27">
         <v>65.507249999999999</v>
@@ -11965,7 +11965,7 @@
         <v>534</v>
       </c>
       <c r="K28" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="L28">
         <v>115.77257062392492</v>
@@ -12000,7 +12000,7 @@
         <v>536</v>
       </c>
       <c r="K29" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="L29">
         <v>18.2196769426582</v>
@@ -12035,7 +12035,7 @@
         <v>538</v>
       </c>
       <c r="K30" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="L30">
         <v>56.340844051935598</v>
@@ -12070,7 +12070,7 @@
         <v>540</v>
       </c>
       <c r="K31" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="L31">
         <v>17.215449395412726</v>
@@ -12105,7 +12105,7 @@
         <v>542</v>
       </c>
       <c r="K32" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="L32">
         <v>30.099997664126345</v>
@@ -12140,7 +12140,7 @@
         <v>544</v>
       </c>
       <c r="K33" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="L33">
         <v>33.688735865274175</v>
@@ -12175,7 +12175,7 @@
         <v>546</v>
       </c>
       <c r="K34" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="L34">
         <v>51.033730360170985</v>
@@ -12210,7 +12210,7 @@
         <v>548</v>
       </c>
       <c r="K35" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="L35">
         <v>96.937146457332247</v>
@@ -12245,7 +12245,7 @@
         <v>550</v>
       </c>
       <c r="K36" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="L36">
         <v>50.741209359452725</v>
@@ -12280,7 +12280,7 @@
         <v>552</v>
       </c>
       <c r="K37" t="s">
-        <v>443</v>
+        <v>414</v>
       </c>
       <c r="L37">
         <v>22.332533209679987</v>
@@ -12315,7 +12315,7 @@
         <v>554</v>
       </c>
       <c r="K38" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L38">
         <v>43.528633223332768</v>
@@ -12330,7 +12330,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67E2C4D2-46DA-428D-BB25-C8F750890F41}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61673D87-0638-4D97-BE8F-9CBFD7BB66FA}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_FRA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CB4EBAD-D9FD-4802-8BA2-06BA1364224B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17307221-E6E5-49B0-A1E9-A6DB011FECA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -939,46 +939,100 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_007</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 7</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_028</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 28</t>
   </si>
   <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
   </si>
   <si>
     <t>distr_solelc_spv_009</t>
@@ -1017,40 +1071,52 @@
     <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
   </si>
   <si>
     <t>distr_solelc_spv_002</t>
@@ -1059,94 +1125,46 @@
     <t>connecting solar to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_dem4</t>
+  </si>
+  <si>
+    <t>e_gen4,e_dem3</t>
+  </si>
+  <si>
+    <t>e_dem3</t>
+  </si>
+  <si>
+    <t>e_dem4,e_gen4</t>
+  </si>
+  <si>
+    <t>e_dem4,e_gen0</t>
+  </si>
+  <si>
     <t>e_dem2,e_gen0,e_gen2</t>
   </si>
   <si>
     <t>e_dem4,e_gen0,e_gen4,e_dem0</t>
   </si>
   <si>
-    <t>e_dem4,e_gen4</t>
-  </si>
-  <si>
-    <t>e_dem4</t>
-  </si>
-  <si>
-    <t>e_gen4,e_dem3</t>
-  </si>
-  <si>
-    <t>e_dem3</t>
+    <t>e_gen4</t>
+  </si>
+  <si>
+    <t>e_dem1,e_gen3</t>
+  </si>
+  <si>
+    <t>e_dem3,e_gen1</t>
+  </si>
+  <si>
+    <t>e_dem0,e_gen3</t>
+  </si>
+  <si>
+    <t>e_gen1,e_dem1</t>
   </si>
   <si>
     <t>e_dem2</t>
@@ -1158,40 +1176,34 @@
     <t>e_gen0,e_dem2,e_dem0</t>
   </si>
   <si>
-    <t>e_dem0,e_gen3</t>
-  </si>
-  <si>
-    <t>e_gen1,e_dem1</t>
-  </si>
-  <si>
-    <t>e_gen4</t>
-  </si>
-  <si>
-    <t>e_dem1,e_gen3</t>
+    <t>e_gen2</t>
+  </si>
+  <si>
+    <t>e_gen1,e_gen3,e_dem1</t>
+  </si>
+  <si>
+    <t>e_gen4,e_gen1</t>
+  </si>
+  <si>
+    <t>e_dem0,e_gen4,e_gen1</t>
+  </si>
+  <si>
+    <t>e_dem0,e_gen2</t>
   </si>
   <si>
     <t>e_gen2,e_dem0</t>
   </si>
   <si>
-    <t>e_dem4,e_gen0</t>
-  </si>
-  <si>
-    <t>e_gen4,e_gen1</t>
-  </si>
-  <si>
-    <t>e_gen2</t>
-  </si>
-  <si>
-    <t>e_gen1,e_gen3,e_dem1</t>
-  </si>
-  <si>
-    <t>e_dem0,e_gen2</t>
-  </si>
-  <si>
-    <t>e_dem0,e_gen4,e_gen1</t>
-  </si>
-  <si>
-    <t>e_dem3,e_gen1</t>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
   </si>
   <si>
     <t>distr_wonelc_won_009</t>
@@ -1206,6 +1218,84 @@
     <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_027</t>
   </si>
   <si>
@@ -1218,10 +1308,40 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_wonelc_won_013</t>
@@ -1242,124 +1362,10 @@
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
   </si>
   <si>
     <t>elc_won_009</t>
@@ -1371,13 +1377,91 @@
     <t>e_gen3,e_dem1</t>
   </si>
   <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_dem2,e_gen2</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_dem2,e_gen0</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_gen4,e_dem0,e_gen1,e_gen3</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_dem1</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_gen0,e_dem4,e_gen4</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
     <t>elc_won_027</t>
   </si>
   <si>
     <t>elc_won_005</t>
   </si>
   <si>
-    <t>elc_won_006</t>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_gen1</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_dem2,e_gen2,e_dem0</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_gen1,e_dem1,e_gen3</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
   </si>
   <si>
     <t>elc_won_013</t>
@@ -1389,88 +1473,46 @@
     <t>elc_won_004</t>
   </si>
   <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_gen1</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_dem1</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_dem2,e_gen2,e_dem0</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_gen1,e_dem1,e_gen3</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_gen0,e_dem4,e_gen4</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_dem2,e_gen2</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_dem2,e_gen0</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_gen4,e_dem0,e_gen1,e_gen3</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
   </si>
   <si>
     <t>distr_wofelc_wof_007</t>
@@ -1479,16 +1521,52 @@
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
     <t>distr_wofelc_wof_013</t>
@@ -1497,136 +1575,58 @@
     <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_gen0,e_dem2,e_dem4</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
   </si>
   <si>
     <t>elc_wof_007</t>
   </si>
   <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
   </si>
   <si>
     <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_gen0,e_dem2,e_dem4</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -6675,7 +6675,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E02236E-7B3E-4AB7-B67F-AF41B09F8BBF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E507BD2A-F064-4EAF-9393-4A84B4A2B20D}">
   <dimension ref="B9:BD40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6913,16 +6913,16 @@
         <v>270</v>
       </c>
       <c r="Y11" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="Z11" t="s">
         <v>334</v>
       </c>
       <c r="AA11">
-        <v>0.99074898552043367</v>
+        <v>0.98943698292665661</v>
       </c>
       <c r="AB11">
-        <v>169.6019321253824</v>
+        <v>193.6553130112959</v>
       </c>
       <c r="AD11" t="s">
         <v>269</v>
@@ -6952,13 +6952,13 @@
         <v>411</v>
       </c>
       <c r="AN11" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="AO11">
-        <v>0.98974092979483974</v>
+        <v>0.99266379654332038</v>
       </c>
       <c r="AP11">
-        <v>188.08295376127217</v>
+        <v>134.49706337246005</v>
       </c>
       <c r="AR11" t="s">
         <v>269</v>
@@ -6988,13 +6988,13 @@
         <v>482</v>
       </c>
       <c r="BB11" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="BC11">
-        <v>0.98987270103949943</v>
+        <v>0.98127791933809161</v>
       </c>
       <c r="BD11">
-        <v>185.6671476091779</v>
+        <v>343.23814546832108</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7059,16 +7059,16 @@
         <v>274</v>
       </c>
       <c r="Y12" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="Z12" t="s">
         <v>335</v>
       </c>
       <c r="AA12">
-        <v>0.98871903666488603</v>
+        <v>0.98844033553992972</v>
       </c>
       <c r="AB12">
-        <v>206.81766114375711</v>
+        <v>211.92718176795447</v>
       </c>
       <c r="AD12" t="s">
         <v>269</v>
@@ -7098,13 +7098,13 @@
         <v>412</v>
       </c>
       <c r="AN12" t="s">
-        <v>413</v>
+        <v>334</v>
       </c>
       <c r="AO12">
-        <v>0.99454803063103558</v>
+        <v>0.99373126046519367</v>
       </c>
       <c r="AP12">
-        <v>99.952771764347304</v>
+        <v>114.92689147144912</v>
       </c>
       <c r="AR12" t="s">
         <v>269</v>
@@ -7134,13 +7134,13 @@
         <v>483</v>
       </c>
       <c r="BB12" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="BC12">
-        <v>0.98127791933809161</v>
+        <v>0.9861533465577601</v>
       </c>
       <c r="BD12">
-        <v>343.23814546832108</v>
+        <v>253.85531310773223</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7205,16 +7205,16 @@
         <v>276</v>
       </c>
       <c r="Y13" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="Z13" t="s">
         <v>336</v>
       </c>
       <c r="AA13">
-        <v>0.99306659504794947</v>
+        <v>0.97057104063486466</v>
       </c>
       <c r="AB13">
-        <v>127.11242412092568</v>
+        <v>539.53092169414879</v>
       </c>
       <c r="AD13" t="s">
         <v>269</v>
@@ -7241,16 +7241,16 @@
         <v>359</v>
       </c>
       <c r="AM13" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AN13" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="AO13">
-        <v>0.99668790123920514</v>
+        <v>0.98974092979483974</v>
       </c>
       <c r="AP13">
-        <v>60.721810614572206</v>
+        <v>188.08295376127217</v>
       </c>
       <c r="AR13" t="s">
         <v>269</v>
@@ -7280,13 +7280,13 @@
         <v>484</v>
       </c>
       <c r="BB13" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="BC13">
-        <v>0.97024476000465243</v>
+        <v>0.98810453029075374</v>
       </c>
       <c r="BD13">
-        <v>545.51273324803913</v>
+        <v>218.08361133618146</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7351,16 +7351,16 @@
         <v>278</v>
       </c>
       <c r="Y14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Z14" t="s">
         <v>337</v>
       </c>
       <c r="AA14">
-        <v>0.98943698292665661</v>
+        <v>0.99306659504794947</v>
       </c>
       <c r="AB14">
-        <v>193.6553130112959</v>
+        <v>127.11242412092568</v>
       </c>
       <c r="AD14" t="s">
         <v>269</v>
@@ -7387,16 +7387,16 @@
         <v>361</v>
       </c>
       <c r="AM14" t="s">
+        <v>414</v>
+      </c>
+      <c r="AN14" t="s">
         <v>415</v>
       </c>
-      <c r="AN14" t="s">
-        <v>339</v>
-      </c>
       <c r="AO14">
-        <v>0.99396981584832544</v>
+        <v>0.99454803063103558</v>
       </c>
       <c r="AP14">
-        <v>110.55337611403426</v>
+        <v>99.952771764347304</v>
       </c>
       <c r="AR14" t="s">
         <v>269</v>
@@ -7426,13 +7426,13 @@
         <v>485</v>
       </c>
       <c r="BB14" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="BC14">
-        <v>0.98470059323114356</v>
+        <v>0.97024476000465243</v>
       </c>
       <c r="BD14">
-        <v>280.48912409570232</v>
+        <v>545.51273324803913</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7497,16 +7497,16 @@
         <v>280</v>
       </c>
       <c r="Y15" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="Z15" t="s">
         <v>338</v>
       </c>
       <c r="AA15">
-        <v>0.98844033553992972</v>
+        <v>0.99132345360703722</v>
       </c>
       <c r="AB15">
-        <v>211.92718176795447</v>
+        <v>159.07001720431779</v>
       </c>
       <c r="AD15" t="s">
         <v>269</v>
@@ -7536,13 +7536,13 @@
         <v>416</v>
       </c>
       <c r="AN15" t="s">
-        <v>354</v>
+        <v>417</v>
       </c>
       <c r="AO15">
-        <v>0.99536525245638341</v>
+        <v>0.98552281783188733</v>
       </c>
       <c r="AP15">
-        <v>84.970371632971023</v>
+        <v>265.41500641539994</v>
       </c>
       <c r="AR15" t="s">
         <v>269</v>
@@ -7643,16 +7643,16 @@
         <v>282</v>
       </c>
       <c r="Y16" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="Z16" t="s">
         <v>339</v>
       </c>
       <c r="AA16">
-        <v>0.97057104063486466</v>
+        <v>0.99074898552043367</v>
       </c>
       <c r="AB16">
-        <v>539.53092169414879</v>
+        <v>169.6019321253824</v>
       </c>
       <c r="AD16" t="s">
         <v>269</v>
@@ -7679,16 +7679,16 @@
         <v>365</v>
       </c>
       <c r="AM16" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN16" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="AO16">
-        <v>0.99568755601261638</v>
+        <v>0.98584846679356541</v>
       </c>
       <c r="AP16">
-        <v>79.061473102033588</v>
+        <v>259.44477545130104</v>
       </c>
       <c r="AR16" t="s">
         <v>269</v>
@@ -7718,13 +7718,13 @@
         <v>488</v>
       </c>
       <c r="BB16" t="s">
-        <v>339</v>
+        <v>417</v>
       </c>
       <c r="BC16">
-        <v>0.96620291469621566</v>
+        <v>0.98430504414907682</v>
       </c>
       <c r="BD16">
-        <v>619.61323056937977</v>
+        <v>287.74085726692596</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7789,16 +7789,16 @@
         <v>284</v>
       </c>
       <c r="Y17" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="Z17" t="s">
         <v>340</v>
       </c>
       <c r="AA17">
-        <v>0.99133738566043939</v>
+        <v>0.98871903666488603</v>
       </c>
       <c r="AB17">
-        <v>158.81459622527697</v>
+        <v>206.81766114375711</v>
       </c>
       <c r="AD17" t="s">
         <v>269</v>
@@ -7825,16 +7825,16 @@
         <v>367</v>
       </c>
       <c r="AM17" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN17" t="s">
-        <v>343</v>
+        <v>420</v>
       </c>
       <c r="AO17">
-        <v>0.99099144211961365</v>
+        <v>0.99296607263934833</v>
       </c>
       <c r="AP17">
-        <v>165.1568944737499</v>
+        <v>128.95533494527976</v>
       </c>
       <c r="AR17" t="s">
         <v>269</v>
@@ -7864,13 +7864,13 @@
         <v>489</v>
       </c>
       <c r="BB17" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="BC17">
-        <v>0.96972263277531634</v>
+        <v>0.99428710319679992</v>
       </c>
       <c r="BD17">
-        <v>555.08506578586628</v>
+        <v>104.7364413920006</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7935,16 +7935,16 @@
         <v>286</v>
       </c>
       <c r="Y18" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="Z18" t="s">
         <v>341</v>
       </c>
       <c r="AA18">
-        <v>0.99560473871467581</v>
+        <v>0.99058732692867291</v>
       </c>
       <c r="AB18">
-        <v>80.579790230943289</v>
+        <v>172.56567297432909</v>
       </c>
       <c r="AD18" t="s">
         <v>269</v>
@@ -7971,16 +7971,16 @@
         <v>369</v>
       </c>
       <c r="AM18" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AN18" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="AO18">
-        <v>0.99702764180837389</v>
+        <v>0.98992222971133592</v>
       </c>
       <c r="AP18">
-        <v>54.493233513145114</v>
+        <v>184.75912195884121</v>
       </c>
       <c r="AR18" t="s">
         <v>269</v>
@@ -8010,13 +8010,13 @@
         <v>490</v>
       </c>
       <c r="BB18" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="BC18">
-        <v>0.96193435381293269</v>
+        <v>0.98987270103949943</v>
       </c>
       <c r="BD18">
-        <v>697.87018009623353</v>
+        <v>185.6671476091779</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8081,16 +8081,16 @@
         <v>288</v>
       </c>
       <c r="Y19" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="Z19" t="s">
         <v>342</v>
       </c>
       <c r="AA19">
-        <v>0.99188284926968906</v>
+        <v>0.99456953758198319</v>
       </c>
       <c r="AB19">
-        <v>148.81443005569966</v>
+        <v>99.558477663641582</v>
       </c>
       <c r="AD19" t="s">
         <v>269</v>
@@ -8117,16 +8117,16 @@
         <v>371</v>
       </c>
       <c r="AM19" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AN19" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="AO19">
-        <v>0.9782800434603014</v>
+        <v>0.99027568948244393</v>
       </c>
       <c r="AP19">
-        <v>398.19920322780678</v>
+        <v>178.27902615519463</v>
       </c>
       <c r="AR19" t="s">
         <v>269</v>
@@ -8156,13 +8156,13 @@
         <v>491</v>
       </c>
       <c r="BB19" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="BC19">
-        <v>0.97296139770869694</v>
+        <v>0.98116881440348735</v>
       </c>
       <c r="BD19">
-        <v>495.70770867388939</v>
+        <v>345.23840260273118</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8227,16 +8227,16 @@
         <v>290</v>
       </c>
       <c r="Y20" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="Z20" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="AA20">
-        <v>0.99628107477919792</v>
+        <v>0.99082744703600512</v>
       </c>
       <c r="AB20">
-        <v>68.180295714705792</v>
+        <v>168.16347100657356</v>
       </c>
       <c r="AD20" t="s">
         <v>269</v>
@@ -8263,16 +8263,16 @@
         <v>373</v>
       </c>
       <c r="AM20" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AN20" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AO20">
-        <v>0.99299955705033549</v>
+        <v>0.98523670671496333</v>
       </c>
       <c r="AP20">
-        <v>128.34145407718299</v>
+        <v>270.66037689233832</v>
       </c>
       <c r="AR20" t="s">
         <v>269</v>
@@ -8302,13 +8302,13 @@
         <v>492</v>
       </c>
       <c r="BB20" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="BC20">
-        <v>0.97519287309306191</v>
+        <v>0.96620291469621566</v>
       </c>
       <c r="BD20">
-        <v>454.79732662719823</v>
+        <v>619.61323056937977</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8373,16 +8373,16 @@
         <v>292</v>
       </c>
       <c r="Y21" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z21" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AA21">
-        <v>0.9922832499015094</v>
+        <v>0.99238998569866288</v>
       </c>
       <c r="AB21">
-        <v>141.47375180566112</v>
+        <v>139.51692885784635</v>
       </c>
       <c r="AD21" t="s">
         <v>269</v>
@@ -8409,16 +8409,16 @@
         <v>375</v>
       </c>
       <c r="AM21" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AN21" t="s">
-        <v>424</v>
+        <v>336</v>
       </c>
       <c r="AO21">
-        <v>0.98967297418060196</v>
+        <v>0.99104096459785573</v>
       </c>
       <c r="AP21">
-        <v>189.3288066889647</v>
+        <v>164.24898237264404</v>
       </c>
       <c r="AR21" t="s">
         <v>269</v>
@@ -8448,13 +8448,13 @@
         <v>493</v>
       </c>
       <c r="BB21" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="BC21">
-        <v>0.97260423035674359</v>
+        <v>0.96972263277531634</v>
       </c>
       <c r="BD21">
-        <v>502.2557767930341</v>
+        <v>555.08506578586628</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8519,16 +8519,16 @@
         <v>294</v>
       </c>
       <c r="Y22" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="Z22" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="AA22">
-        <v>0.99427514814587914</v>
+        <v>0.99380321394043492</v>
       </c>
       <c r="AB22">
-        <v>104.95561732554863</v>
+        <v>113.60774442536065</v>
       </c>
       <c r="AD22" t="s">
         <v>269</v>
@@ -8555,16 +8555,16 @@
         <v>377</v>
       </c>
       <c r="AM22" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN22" t="s">
-        <v>337</v>
+        <v>427</v>
       </c>
       <c r="AO22">
-        <v>0.99266379654332038</v>
+        <v>0.99260627833960313</v>
       </c>
       <c r="AP22">
-        <v>134.49706337246005</v>
+        <v>135.55156377394354</v>
       </c>
       <c r="AR22" t="s">
         <v>269</v>
@@ -8594,13 +8594,13 @@
         <v>494</v>
       </c>
       <c r="BB22" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="BC22">
-        <v>0.98578667690837229</v>
+        <v>0.96193435381293269</v>
       </c>
       <c r="BD22">
-        <v>260.57759001317498</v>
+        <v>697.87018009623353</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8665,16 +8665,16 @@
         <v>296</v>
       </c>
       <c r="Y23" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Z23" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="AA23">
-        <v>0.99380321394043492</v>
+        <v>0.98950922221532345</v>
       </c>
       <c r="AB23">
-        <v>113.60774442536065</v>
+        <v>192.33092605240353</v>
       </c>
       <c r="AD23" t="s">
         <v>269</v>
@@ -8701,16 +8701,16 @@
         <v>379</v>
       </c>
       <c r="AM23" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AN23" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AO23">
-        <v>0.99373126046519367</v>
+        <v>0.98220670102649277</v>
       </c>
       <c r="AP23">
-        <v>114.92689147144912</v>
+        <v>326.21048118096536</v>
       </c>
       <c r="AR23" t="s">
         <v>269</v>
@@ -8740,13 +8740,13 @@
         <v>495</v>
       </c>
       <c r="BB23" t="s">
-        <v>437</v>
+        <v>346</v>
       </c>
       <c r="BC23">
-        <v>0.98430504414907682</v>
+        <v>0.97296139770869694</v>
       </c>
       <c r="BD23">
-        <v>287.74085726692596</v>
+        <v>495.70770867388939</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8811,16 +8811,16 @@
         <v>298</v>
       </c>
       <c r="Y24" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Z24" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AA24">
-        <v>0.98950922221532345</v>
+        <v>0.99361327661798182</v>
       </c>
       <c r="AB24">
-        <v>192.33092605240353</v>
+        <v>117.08992867033326</v>
       </c>
       <c r="AD24" t="s">
         <v>269</v>
@@ -8847,16 +8847,16 @@
         <v>381</v>
       </c>
       <c r="AM24" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AN24" t="s">
-        <v>336</v>
+        <v>430</v>
       </c>
       <c r="AO24">
-        <v>0.99102447886015177</v>
+        <v>0.98980925931588959</v>
       </c>
       <c r="AP24">
-        <v>164.55122089721749</v>
+        <v>186.83024587535752</v>
       </c>
       <c r="AR24" t="s">
         <v>269</v>
@@ -8886,13 +8886,13 @@
         <v>496</v>
       </c>
       <c r="BB24" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="BC24">
-        <v>0.99428710319679992</v>
+        <v>0.97519287309306191</v>
       </c>
       <c r="BD24">
-        <v>104.7364413920006</v>
+        <v>454.79732662719823</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8957,16 +8957,16 @@
         <v>300</v>
       </c>
       <c r="Y25" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="Z25" t="s">
         <v>345</v>
       </c>
       <c r="AA25">
-        <v>0.99058732692867291</v>
+        <v>0.99105162171633221</v>
       </c>
       <c r="AB25">
-        <v>172.56567297432909</v>
+        <v>164.05360186724374</v>
       </c>
       <c r="AD25" t="s">
         <v>269</v>
@@ -8993,16 +8993,16 @@
         <v>383</v>
       </c>
       <c r="AM25" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="AN25" t="s">
-        <v>429</v>
+        <v>344</v>
       </c>
       <c r="AO25">
-        <v>0.99265977528547111</v>
+        <v>0.99194279509442385</v>
       </c>
       <c r="AP25">
-        <v>134.57078643303035</v>
+        <v>147.71542326889627</v>
       </c>
       <c r="AR25" t="s">
         <v>269</v>
@@ -9032,13 +9032,13 @@
         <v>497</v>
       </c>
       <c r="BB25" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="BC25">
-        <v>0.9861533465577601</v>
+        <v>0.97260423035674359</v>
       </c>
       <c r="BD25">
-        <v>253.85531310773223</v>
+        <v>502.2557767930341</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9103,16 +9103,16 @@
         <v>302</v>
       </c>
       <c r="Y26" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Z26" t="s">
         <v>346</v>
       </c>
       <c r="AA26">
-        <v>0.99456953758198319</v>
+        <v>0.99133738566043939</v>
       </c>
       <c r="AB26">
-        <v>99.558477663641582</v>
+        <v>158.81459622527697</v>
       </c>
       <c r="AD26" t="s">
         <v>269</v>
@@ -9139,16 +9139,16 @@
         <v>385</v>
       </c>
       <c r="AM26" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AN26" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="AO26">
-        <v>0.99102919755488506</v>
+        <v>0.9947696749839372</v>
       </c>
       <c r="AP26">
-        <v>164.46471149377308</v>
+        <v>95.889291961151685</v>
       </c>
       <c r="AR26" t="s">
         <v>269</v>
@@ -9178,13 +9178,13 @@
         <v>498</v>
       </c>
       <c r="BB26" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="BC26">
-        <v>0.98810453029075374</v>
+        <v>0.98578667690837229</v>
       </c>
       <c r="BD26">
-        <v>218.08361133618146</v>
+        <v>260.57759001317498</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9249,16 +9249,16 @@
         <v>304</v>
       </c>
       <c r="Y27" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="Z27" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="AA27">
-        <v>0.99361327661798182</v>
+        <v>0.99560473871467581</v>
       </c>
       <c r="AB27">
-        <v>117.08992867033326</v>
+        <v>80.579790230943289</v>
       </c>
       <c r="AD27" t="s">
         <v>269</v>
@@ -9285,16 +9285,16 @@
         <v>387</v>
       </c>
       <c r="AM27" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN27" t="s">
-        <v>433</v>
+        <v>343</v>
       </c>
       <c r="AO27">
-        <v>0.98980925931588959</v>
+        <v>0.99536525245638341</v>
       </c>
       <c r="AP27">
-        <v>186.83024587535752</v>
+        <v>84.970371632971023</v>
       </c>
       <c r="AR27" t="s">
         <v>269</v>
@@ -9324,13 +9324,13 @@
         <v>499</v>
       </c>
       <c r="BB27" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="BC27">
-        <v>0.98116881440348735</v>
+        <v>0.98470059323114356</v>
       </c>
       <c r="BD27">
-        <v>345.23840260273118</v>
+        <v>280.48912409570232</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9395,16 +9395,16 @@
         <v>306</v>
       </c>
       <c r="Y28" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Z28" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="AA28">
-        <v>0.99105162171633221</v>
+        <v>0.99188284926968906</v>
       </c>
       <c r="AB28">
-        <v>164.05360186724374</v>
+        <v>148.81443005569966</v>
       </c>
       <c r="AD28" t="s">
         <v>269</v>
@@ -9434,13 +9434,13 @@
         <v>434</v>
       </c>
       <c r="AN28" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="AO28">
-        <v>0.99194279509442385</v>
+        <v>0.99668790123920514</v>
       </c>
       <c r="AP28">
-        <v>147.71542326889627</v>
+        <v>60.721810614572206</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9505,16 +9505,16 @@
         <v>308</v>
       </c>
       <c r="Y29" t="s">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="Z29" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="AA29">
-        <v>0.99203796026218938</v>
+        <v>0.99628107477919792</v>
       </c>
       <c r="AB29">
-        <v>145.97072852652775</v>
+        <v>68.180295714705792</v>
       </c>
       <c r="AD29" t="s">
         <v>269</v>
@@ -9544,13 +9544,13 @@
         <v>435</v>
       </c>
       <c r="AN29" t="s">
-        <v>424</v>
+        <v>336</v>
       </c>
       <c r="AO29">
-        <v>0.9947696749839372</v>
+        <v>0.99396981584832544</v>
       </c>
       <c r="AP29">
-        <v>95.889291961151685</v>
+        <v>110.55337611403426</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9615,16 +9615,16 @@
         <v>310</v>
       </c>
       <c r="Y30" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="Z30" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="AA30">
-        <v>0.99132345360703722</v>
+        <v>0.9922832499015094</v>
       </c>
       <c r="AB30">
-        <v>159.07001720431779</v>
+        <v>141.47375180566112</v>
       </c>
       <c r="AD30" t="s">
         <v>269</v>
@@ -9654,13 +9654,13 @@
         <v>436</v>
       </c>
       <c r="AN30" t="s">
-        <v>437</v>
+        <v>337</v>
       </c>
       <c r="AO30">
-        <v>0.98552281783188733</v>
+        <v>0.99102447886015177</v>
       </c>
       <c r="AP30">
-        <v>265.41500641539994</v>
+        <v>164.55122089721749</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9725,16 +9725,16 @@
         <v>312</v>
       </c>
       <c r="Y31" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="Z31" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="AA31">
-        <v>0.99036558192019719</v>
+        <v>0.99427514814587914</v>
       </c>
       <c r="AB31">
-        <v>176.63099812971814</v>
+        <v>104.95561732554863</v>
       </c>
       <c r="AD31" t="s">
         <v>269</v>
@@ -9761,16 +9761,16 @@
         <v>395</v>
       </c>
       <c r="AM31" t="s">
+        <v>437</v>
+      </c>
+      <c r="AN31" t="s">
         <v>438</v>
       </c>
-      <c r="AN31" t="s">
-        <v>337</v>
-      </c>
       <c r="AO31">
-        <v>0.98584846679356541</v>
+        <v>0.99299955705033549</v>
       </c>
       <c r="AP31">
-        <v>259.44477545130104</v>
+        <v>128.34145407718299</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9838,7 +9838,7 @@
         <v>245</v>
       </c>
       <c r="Z32" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="AA32">
         <v>0.98066337855689323</v>
@@ -9874,13 +9874,13 @@
         <v>439</v>
       </c>
       <c r="AN32" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="AO32">
-        <v>0.99296607263934833</v>
+        <v>0.98967297418060196</v>
       </c>
       <c r="AP32">
-        <v>128.95533494527976</v>
+        <v>189.3288066889647</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9948,7 +9948,7 @@
         <v>240</v>
       </c>
       <c r="Z33" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AA33">
         <v>0.99010316852626312</v>
@@ -9981,16 +9981,16 @@
         <v>399</v>
       </c>
       <c r="AM33" t="s">
+        <v>440</v>
+      </c>
+      <c r="AN33" t="s">
         <v>441</v>
       </c>
-      <c r="AN33" t="s">
-        <v>336</v>
-      </c>
       <c r="AO33">
-        <v>0.98992222971133592</v>
+        <v>0.99265977528547111</v>
       </c>
       <c r="AP33">
-        <v>184.75912195884121</v>
+        <v>134.57078643303035</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -10058,7 +10058,7 @@
         <v>260</v>
       </c>
       <c r="Z34" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AA34">
         <v>0.98887858934711803</v>
@@ -10094,13 +10094,13 @@
         <v>442</v>
       </c>
       <c r="AN34" t="s">
-        <v>338</v>
+        <v>443</v>
       </c>
       <c r="AO34">
-        <v>0.99027568948244393</v>
+        <v>0.99102919755488506</v>
       </c>
       <c r="AP34">
-        <v>178.27902615519463</v>
+        <v>164.46471149377308</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -10165,16 +10165,16 @@
         <v>320</v>
       </c>
       <c r="Y35" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Z35" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="AA35">
-        <v>0.99592139175292038</v>
+        <v>0.99455764054307205</v>
       </c>
       <c r="AB35">
-        <v>74.774484529793384</v>
+        <v>99.77659004367905</v>
       </c>
       <c r="AD35" t="s">
         <v>269</v>
@@ -10201,16 +10201,16 @@
         <v>403</v>
       </c>
       <c r="AM35" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN35" t="s">
-        <v>444</v>
+        <v>336</v>
       </c>
       <c r="AO35">
-        <v>0.98523670671496333</v>
+        <v>0.9782800434603014</v>
       </c>
       <c r="AP35">
-        <v>270.66037689233832</v>
+        <v>398.19920322780678</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -10275,16 +10275,16 @@
         <v>322</v>
       </c>
       <c r="Y36" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="Z36" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AA36">
-        <v>0.99455764054307205</v>
+        <v>0.99510234843435064</v>
       </c>
       <c r="AB36">
-        <v>99.77659004367905</v>
+        <v>89.790278703571531</v>
       </c>
       <c r="AD36" t="s">
         <v>269</v>
@@ -10314,13 +10314,13 @@
         <v>445</v>
       </c>
       <c r="AN36" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AO36">
-        <v>0.99104096459785573</v>
+        <v>0.99568755601261638</v>
       </c>
       <c r="AP36">
-        <v>164.24898237264404</v>
+        <v>79.061473102033588</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -10385,16 +10385,16 @@
         <v>324</v>
       </c>
       <c r="Y37" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Z37" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AA37">
-        <v>0.99510234843435064</v>
+        <v>0.98506785527064555</v>
       </c>
       <c r="AB37">
-        <v>89.790278703571531</v>
+        <v>273.75598670483231</v>
       </c>
       <c r="AD37" t="s">
         <v>269</v>
@@ -10424,13 +10424,13 @@
         <v>446</v>
       </c>
       <c r="AN37" t="s">
-        <v>424</v>
+        <v>344</v>
       </c>
       <c r="AO37">
-        <v>0.99260627833960313</v>
+        <v>0.99099144211961365</v>
       </c>
       <c r="AP37">
-        <v>135.55156377394354</v>
+        <v>165.1568944737499</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10495,16 +10495,16 @@
         <v>326</v>
       </c>
       <c r="Y38" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="Z38" t="s">
         <v>353</v>
       </c>
       <c r="AA38">
-        <v>0.98506785527064555</v>
+        <v>0.99592139175292038</v>
       </c>
       <c r="AB38">
-        <v>273.75598670483231</v>
+        <v>74.774484529793384</v>
       </c>
       <c r="AD38" t="s">
         <v>269</v>
@@ -10534,13 +10534,13 @@
         <v>447</v>
       </c>
       <c r="AN38" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AO38">
-        <v>0.98220670102649277</v>
+        <v>0.99702764180837389</v>
       </c>
       <c r="AP38">
-        <v>326.21048118096536</v>
+        <v>54.493233513145114</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -10605,16 +10605,16 @@
         <v>328</v>
       </c>
       <c r="Y39" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="Z39" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="AA39">
-        <v>0.99082744703600512</v>
+        <v>0.99036558192019719</v>
       </c>
       <c r="AB39">
-        <v>168.16347100657356</v>
+        <v>176.63099812971814</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -10679,16 +10679,16 @@
         <v>330</v>
       </c>
       <c r="Y40" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="Z40" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="AA40">
-        <v>0.99238998569866288</v>
+        <v>0.99203796026218938</v>
       </c>
       <c r="AB40">
-        <v>139.51692885784635</v>
+        <v>145.97072852652775</v>
       </c>
     </row>
   </sheetData>
@@ -10697,7 +10697,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C9E5246-6D5D-4A7F-8DA7-87655161E1F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43720E71-E287-46FB-9202-0A5FF9046758}">
   <dimension ref="B9:Z38"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10809,7 +10809,7 @@
         <v>500</v>
       </c>
       <c r="K11" t="s">
-        <v>420</v>
+        <v>444</v>
       </c>
       <c r="L11">
         <v>7.5384385218371168</v>
@@ -10842,7 +10842,7 @@
         <v>556</v>
       </c>
       <c r="X11" t="s">
-        <v>498</v>
+        <v>484</v>
       </c>
       <c r="Y11">
         <v>38.411999999999999</v>
@@ -10877,7 +10877,7 @@
         <v>502</v>
       </c>
       <c r="K12" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="L12">
         <v>8.5464211426904182</v>
@@ -10910,7 +10910,7 @@
         <v>558</v>
       </c>
       <c r="X12" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="Y12">
         <v>9.3112499999999994</v>
@@ -10945,7 +10945,7 @@
         <v>504</v>
       </c>
       <c r="K13" t="s">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="L13">
         <v>1.5340845206129941</v>
@@ -10978,7 +10978,7 @@
         <v>560</v>
       </c>
       <c r="X13" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="Y13">
         <v>9.5287500000000005</v>
@@ -11013,7 +11013,7 @@
         <v>506</v>
       </c>
       <c r="K14" t="s">
-        <v>419</v>
+        <v>447</v>
       </c>
       <c r="L14">
         <v>17.766367792804527</v>
@@ -11046,7 +11046,7 @@
         <v>562</v>
       </c>
       <c r="X14" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="Y14">
         <v>2.1749999999999999E-2</v>
@@ -11081,7 +11081,7 @@
         <v>508</v>
       </c>
       <c r="K15" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="L15">
         <v>3.7020770759557711</v>
@@ -11114,7 +11114,7 @@
         <v>564</v>
       </c>
       <c r="X15" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="Y15">
         <v>8.2590000000000003</v>
@@ -11149,7 +11149,7 @@
         <v>510</v>
       </c>
       <c r="K16" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="L16">
         <v>28.612118601835597</v>
@@ -11182,7 +11182,7 @@
         <v>566</v>
       </c>
       <c r="X16" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="Y16">
         <v>0.40575</v>
@@ -11217,7 +11217,7 @@
         <v>512</v>
       </c>
       <c r="K17" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="L17">
         <v>54.523871060763341</v>
@@ -11250,7 +11250,7 @@
         <v>568</v>
       </c>
       <c r="X17" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="Y17">
         <v>6.4290000000000003</v>
@@ -11285,7 +11285,7 @@
         <v>514</v>
       </c>
       <c r="K18" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="L18">
         <v>21.752928174024966</v>
@@ -11318,7 +11318,7 @@
         <v>570</v>
       </c>
       <c r="X18" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="Y18">
         <v>0.10199999999999999</v>
@@ -11353,7 +11353,7 @@
         <v>516</v>
       </c>
       <c r="K19" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L19">
         <v>75.839981284454382</v>
@@ -11386,7 +11386,7 @@
         <v>572</v>
       </c>
       <c r="X19" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="Y19">
         <v>27.910499999999999</v>
@@ -11421,7 +11421,7 @@
         <v>518</v>
       </c>
       <c r="K20" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="L20">
         <v>15.373849239963436</v>
@@ -11454,7 +11454,7 @@
         <v>574</v>
       </c>
       <c r="X20" t="s">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="Y20">
         <v>2.7322500000000001</v>
@@ -11489,7 +11489,7 @@
         <v>520</v>
       </c>
       <c r="K21" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="L21">
         <v>20.941488433116</v>
@@ -11557,7 +11557,7 @@
         <v>522</v>
       </c>
       <c r="K22" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="L22">
         <v>10.348692721070078</v>
@@ -11590,7 +11590,7 @@
         <v>578</v>
       </c>
       <c r="X22" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="Y22">
         <v>80.700749999999999</v>
@@ -11625,7 +11625,7 @@
         <v>524</v>
       </c>
       <c r="K23" t="s">
-        <v>417</v>
+        <v>445</v>
       </c>
       <c r="L23">
         <v>30.807418987588004</v>
@@ -11658,7 +11658,7 @@
         <v>580</v>
       </c>
       <c r="X23" t="s">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="Y23">
         <v>19.849499999999999</v>
@@ -11693,7 +11693,7 @@
         <v>526</v>
       </c>
       <c r="K24" t="s">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="L24">
         <v>6.8734480919946561</v>
@@ -11726,7 +11726,7 @@
         <v>582</v>
       </c>
       <c r="X24" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="Y24">
         <v>35.221499999999999</v>
@@ -11761,7 +11761,7 @@
         <v>528</v>
       </c>
       <c r="K25" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="L25">
         <v>45.970542554915504</v>
@@ -11794,7 +11794,7 @@
         <v>584</v>
       </c>
       <c r="X25" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="Y25">
         <v>88.549499999999995</v>
@@ -11829,7 +11829,7 @@
         <v>530</v>
       </c>
       <c r="K26" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="L26">
         <v>102.16105468063856</v>
@@ -11862,7 +11862,7 @@
         <v>586</v>
       </c>
       <c r="X26" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="Y26">
         <v>42.073500000000003</v>
@@ -11897,7 +11897,7 @@
         <v>532</v>
       </c>
       <c r="K27" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="L27">
         <v>33.663807794729088</v>
@@ -11930,7 +11930,7 @@
         <v>588</v>
       </c>
       <c r="X27" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="Y27">
         <v>65.507249999999999</v>
@@ -11965,7 +11965,7 @@
         <v>534</v>
       </c>
       <c r="K28" t="s">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="L28">
         <v>115.77257062392492</v>
@@ -12000,7 +12000,7 @@
         <v>536</v>
       </c>
       <c r="K29" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="L29">
         <v>18.2196769426582</v>
@@ -12035,7 +12035,7 @@
         <v>538</v>
       </c>
       <c r="K30" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L30">
         <v>56.340844051935598</v>
@@ -12070,7 +12070,7 @@
         <v>540</v>
       </c>
       <c r="K31" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="L31">
         <v>17.215449395412726</v>
@@ -12105,7 +12105,7 @@
         <v>542</v>
       </c>
       <c r="K32" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="L32">
         <v>30.099997664126345</v>
@@ -12140,7 +12140,7 @@
         <v>544</v>
       </c>
       <c r="K33" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="L33">
         <v>33.688735865274175</v>
@@ -12175,7 +12175,7 @@
         <v>546</v>
       </c>
       <c r="K34" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="L34">
         <v>51.033730360170985</v>
@@ -12210,7 +12210,7 @@
         <v>548</v>
       </c>
       <c r="K35" t="s">
-        <v>418</v>
+        <v>446</v>
       </c>
       <c r="L35">
         <v>96.937146457332247</v>
@@ -12245,7 +12245,7 @@
         <v>550</v>
       </c>
       <c r="K36" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="L36">
         <v>50.741209359452725</v>
@@ -12280,7 +12280,7 @@
         <v>552</v>
       </c>
       <c r="K37" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="L37">
         <v>22.332533209679987</v>
@@ -12315,7 +12315,7 @@
         <v>554</v>
       </c>
       <c r="K38" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="L38">
         <v>43.528633223332768</v>
@@ -12330,7 +12330,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61673D87-0638-4D97-BE8F-9CBFD7BB66FA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74B9B09D-A947-4333-B8C6-B20E06901124}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_FRA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17307221-E6E5-49B0-A1E9-A6DB011FECA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E4EAC4B-8D48-49C9-91E8-7941D3F813EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -939,18 +939,174 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_025</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 25</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_016</t>
   </si>
   <si>
@@ -963,235 +1119,115 @@
     <t>connecting solar to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_001</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_dem4,e_gen4</t>
+  </si>
+  <si>
+    <t>e_dem0,e_gen3</t>
+  </si>
+  <si>
+    <t>e_gen1,e_dem1</t>
+  </si>
+  <si>
+    <t>e_dem2</t>
+  </si>
+  <si>
+    <t>e_gen2</t>
+  </si>
+  <si>
+    <t>e_gen1,e_gen3,e_dem1</t>
+  </si>
+  <si>
+    <t>e_gen4,e_dem3</t>
+  </si>
+  <si>
+    <t>e_gen0,e_dem2</t>
+  </si>
+  <si>
+    <t>e_gen0,e_dem2,e_dem0</t>
+  </si>
+  <si>
     <t>e_dem4</t>
   </si>
   <si>
-    <t>e_gen4,e_dem3</t>
+    <t>e_gen4,e_gen1</t>
+  </si>
+  <si>
+    <t>e_dem0,e_gen4,e_gen1</t>
+  </si>
+  <si>
+    <t>e_dem4,e_gen0</t>
+  </si>
+  <si>
+    <t>e_dem3,e_gen1</t>
+  </si>
+  <si>
+    <t>e_dem1,e_gen3</t>
+  </si>
+  <si>
+    <t>e_gen4</t>
+  </si>
+  <si>
+    <t>e_gen2,e_dem0</t>
+  </si>
+  <si>
+    <t>e_dem2,e_gen0,e_gen2</t>
+  </si>
+  <si>
+    <t>e_dem4,e_gen0,e_gen4,e_dem0</t>
   </si>
   <si>
     <t>e_dem3</t>
   </si>
   <si>
-    <t>e_dem4,e_gen4</t>
-  </si>
-  <si>
-    <t>e_dem4,e_gen0</t>
-  </si>
-  <si>
-    <t>e_dem2,e_gen0,e_gen2</t>
-  </si>
-  <si>
-    <t>e_dem4,e_gen0,e_gen4,e_dem0</t>
-  </si>
-  <si>
-    <t>e_gen4</t>
-  </si>
-  <si>
-    <t>e_dem1,e_gen3</t>
-  </si>
-  <si>
-    <t>e_dem3,e_gen1</t>
-  </si>
-  <si>
-    <t>e_dem0,e_gen3</t>
-  </si>
-  <si>
-    <t>e_gen1,e_dem1</t>
-  </si>
-  <si>
-    <t>e_dem2</t>
-  </si>
-  <si>
-    <t>e_gen0,e_dem2</t>
-  </si>
-  <si>
-    <t>e_gen0,e_dem2,e_dem0</t>
-  </si>
-  <si>
-    <t>e_gen2</t>
-  </si>
-  <si>
-    <t>e_gen1,e_gen3,e_dem1</t>
-  </si>
-  <si>
-    <t>e_gen4,e_gen1</t>
-  </si>
-  <si>
-    <t>e_dem0,e_gen4,e_gen1</t>
-  </si>
-  <si>
     <t>e_dem0,e_gen2</t>
   </si>
   <si>
-    <t>e_gen2,e_dem0</t>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
     <t>distr_wonelc_won_010</t>
@@ -1206,6 +1242,102 @@
     <t>connecting wind onshore to buses in cluster 11</t>
   </si>
   <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_009</t>
   </si>
   <si>
@@ -1218,84 +1350,6 @@
     <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_027</t>
   </si>
   <si>
@@ -1308,58 +1362,31 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_dem2,e_gen2,e_dem0</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_gen1,e_dem1,e_gen3</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_dem2,e_gen2</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
   </si>
   <si>
     <t>elc_won_010</t>
@@ -1368,6 +1395,69 @@
     <t>elc_won_011</t>
   </si>
   <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_gen0,e_dem4,e_gen4</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_dem1</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_gen1</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_dem2,e_gen0</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_gen4,e_dem0,e_gen1,e_gen3</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
     <t>elc_won_009</t>
   </si>
   <si>
@@ -1377,100 +1467,40 @@
     <t>e_gen3,e_dem1</t>
   </si>
   <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_dem2,e_gen2</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_dem2,e_gen0</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_gen4,e_dem0,e_gen1,e_gen3</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_dem1</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_gen0,e_dem4,e_gen4</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
     <t>elc_won_027</t>
   </si>
   <si>
     <t>elc_won_005</t>
   </si>
   <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_gen1</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_dem2,e_gen2,e_dem0</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_gen1,e_dem1,e_gen3</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
   </si>
   <si>
     <t>distr_wofelc_wof_012</t>
@@ -1479,6 +1509,42 @@
     <t>connecting wind offshore to buses in cluster 12</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_010</t>
   </si>
   <si>
@@ -1491,72 +1557,6 @@
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_015</t>
   </si>
   <si>
@@ -1575,49 +1575,49 @@
     <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_gen0,e_dem2,e_dem4</t>
+  </si>
+  <si>
     <t>elc_wof_012</t>
   </si>
   <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
     <t>elc_wof_010</t>
   </si>
   <si>
     <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_gen0,e_dem2,e_dem4</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
   </si>
   <si>
     <t>elc_wof_015</t>
@@ -6675,7 +6675,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E507BD2A-F064-4EAF-9393-4A84B4A2B20D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E8D0AD3-E100-47DE-AE76-8D057DD65D98}">
   <dimension ref="B9:BD40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6913,16 +6913,16 @@
         <v>270</v>
       </c>
       <c r="Y11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Z11" t="s">
         <v>334</v>
       </c>
       <c r="AA11">
-        <v>0.98943698292665661</v>
+        <v>0.99306659504794947</v>
       </c>
       <c r="AB11">
-        <v>193.6553130112959</v>
+        <v>127.11242412092568</v>
       </c>
       <c r="AD11" t="s">
         <v>269</v>
@@ -6952,13 +6952,13 @@
         <v>411</v>
       </c>
       <c r="AN11" t="s">
-        <v>334</v>
+        <v>412</v>
       </c>
       <c r="AO11">
-        <v>0.99266379654332038</v>
+        <v>0.99265977528547111</v>
       </c>
       <c r="AP11">
-        <v>134.49706337246005</v>
+        <v>134.57078643303035</v>
       </c>
       <c r="AR11" t="s">
         <v>269</v>
@@ -6988,13 +6988,13 @@
         <v>482</v>
       </c>
       <c r="BB11" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="BC11">
-        <v>0.98127791933809161</v>
+        <v>0.97024476000465243</v>
       </c>
       <c r="BD11">
-        <v>343.23814546832108</v>
+        <v>545.51273324803913</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7059,16 +7059,16 @@
         <v>274</v>
       </c>
       <c r="Y12" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Z12" t="s">
         <v>335</v>
       </c>
       <c r="AA12">
-        <v>0.98844033553992972</v>
+        <v>0.99361327661798182</v>
       </c>
       <c r="AB12">
-        <v>211.92718176795447</v>
+        <v>117.08992867033326</v>
       </c>
       <c r="AD12" t="s">
         <v>269</v>
@@ -7095,16 +7095,16 @@
         <v>357</v>
       </c>
       <c r="AM12" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AN12" t="s">
-        <v>334</v>
+        <v>414</v>
       </c>
       <c r="AO12">
-        <v>0.99373126046519367</v>
+        <v>0.99102919755488506</v>
       </c>
       <c r="AP12">
-        <v>114.92689147144912</v>
+        <v>164.46471149377308</v>
       </c>
       <c r="AR12" t="s">
         <v>269</v>
@@ -7134,13 +7134,13 @@
         <v>483</v>
       </c>
       <c r="BB12" t="s">
-        <v>334</v>
+        <v>418</v>
       </c>
       <c r="BC12">
-        <v>0.9861533465577601</v>
+        <v>0.98430504414907682</v>
       </c>
       <c r="BD12">
-        <v>253.85531310773223</v>
+        <v>287.74085726692596</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7205,16 +7205,16 @@
         <v>276</v>
       </c>
       <c r="Y13" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Z13" t="s">
         <v>336</v>
       </c>
       <c r="AA13">
-        <v>0.97057104063486466</v>
+        <v>0.99105162171633221</v>
       </c>
       <c r="AB13">
-        <v>539.53092169414879</v>
+        <v>164.05360186724374</v>
       </c>
       <c r="AD13" t="s">
         <v>269</v>
@@ -7241,16 +7241,16 @@
         <v>359</v>
       </c>
       <c r="AM13" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AN13" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AO13">
-        <v>0.98974092979483974</v>
+        <v>0.9782800434603014</v>
       </c>
       <c r="AP13">
-        <v>188.08295376127217</v>
+        <v>398.19920322780678</v>
       </c>
       <c r="AR13" t="s">
         <v>269</v>
@@ -7280,13 +7280,13 @@
         <v>484</v>
       </c>
       <c r="BB13" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="BC13">
-        <v>0.98810453029075374</v>
+        <v>0.99428710319679992</v>
       </c>
       <c r="BD13">
-        <v>218.08361133618146</v>
+        <v>104.7364413920006</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7351,16 +7351,16 @@
         <v>278</v>
       </c>
       <c r="Y14" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="Z14" t="s">
         <v>337</v>
       </c>
       <c r="AA14">
-        <v>0.99306659504794947</v>
+        <v>0.98066337855689323</v>
       </c>
       <c r="AB14">
-        <v>127.11242412092568</v>
+        <v>354.5047264569576</v>
       </c>
       <c r="AD14" t="s">
         <v>269</v>
@@ -7387,16 +7387,16 @@
         <v>361</v>
       </c>
       <c r="AM14" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AN14" t="s">
-        <v>415</v>
+        <v>347</v>
       </c>
       <c r="AO14">
-        <v>0.99454803063103558</v>
+        <v>0.99536525245638341</v>
       </c>
       <c r="AP14">
-        <v>99.952771764347304</v>
+        <v>84.970371632971023</v>
       </c>
       <c r="AR14" t="s">
         <v>269</v>
@@ -7426,13 +7426,13 @@
         <v>485</v>
       </c>
       <c r="BB14" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="BC14">
-        <v>0.97024476000465243</v>
+        <v>0.98116881440348735</v>
       </c>
       <c r="BD14">
-        <v>545.51273324803913</v>
+        <v>345.23840260273118</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7497,16 +7497,16 @@
         <v>280</v>
       </c>
       <c r="Y15" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="Z15" t="s">
         <v>338</v>
       </c>
       <c r="AA15">
-        <v>0.99132345360703722</v>
+        <v>0.99010316852626312</v>
       </c>
       <c r="AB15">
-        <v>159.07001720431779</v>
+        <v>181.44191035184215</v>
       </c>
       <c r="AD15" t="s">
         <v>269</v>
@@ -7533,10 +7533,10 @@
         <v>363</v>
       </c>
       <c r="AM15" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN15" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO15">
         <v>0.98552281783188733</v>
@@ -7643,16 +7643,16 @@
         <v>282</v>
       </c>
       <c r="Y16" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="Z16" t="s">
         <v>339</v>
       </c>
       <c r="AA16">
-        <v>0.99074898552043367</v>
+        <v>0.98887858934711803</v>
       </c>
       <c r="AB16">
-        <v>169.6019321253824</v>
+        <v>203.89252863617014</v>
       </c>
       <c r="AD16" t="s">
         <v>269</v>
@@ -7679,10 +7679,10 @@
         <v>365</v>
       </c>
       <c r="AM16" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN16" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="AO16">
         <v>0.98584846679356541</v>
@@ -7718,13 +7718,13 @@
         <v>488</v>
       </c>
       <c r="BB16" t="s">
-        <v>417</v>
+        <v>337</v>
       </c>
       <c r="BC16">
-        <v>0.98430504414907682</v>
+        <v>0.98127791933809161</v>
       </c>
       <c r="BD16">
-        <v>287.74085726692596</v>
+        <v>343.23814546832108</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7789,16 +7789,16 @@
         <v>284</v>
       </c>
       <c r="Y17" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="Z17" t="s">
         <v>340</v>
       </c>
       <c r="AA17">
-        <v>0.98871903666488603</v>
+        <v>0.99380321394043492</v>
       </c>
       <c r="AB17">
-        <v>206.81766114375711</v>
+        <v>113.60774442536065</v>
       </c>
       <c r="AD17" t="s">
         <v>269</v>
@@ -7825,16 +7825,16 @@
         <v>367</v>
       </c>
       <c r="AM17" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN17" t="s">
-        <v>420</v>
+        <v>343</v>
       </c>
       <c r="AO17">
-        <v>0.99296607263934833</v>
+        <v>0.99266379654332038</v>
       </c>
       <c r="AP17">
-        <v>128.95533494527976</v>
+        <v>134.49706337246005</v>
       </c>
       <c r="AR17" t="s">
         <v>269</v>
@@ -7864,13 +7864,13 @@
         <v>489</v>
       </c>
       <c r="BB17" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="BC17">
-        <v>0.99428710319679992</v>
+        <v>0.98987270103949943</v>
       </c>
       <c r="BD17">
-        <v>104.7364413920006</v>
+        <v>185.6671476091779</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7935,16 +7935,16 @@
         <v>286</v>
       </c>
       <c r="Y18" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="Z18" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="AA18">
-        <v>0.99058732692867291</v>
+        <v>0.98950922221532345</v>
       </c>
       <c r="AB18">
-        <v>172.56567297432909</v>
+        <v>192.33092605240353</v>
       </c>
       <c r="AD18" t="s">
         <v>269</v>
@@ -7974,13 +7974,13 @@
         <v>421</v>
       </c>
       <c r="AN18" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="AO18">
-        <v>0.98992222971133592</v>
+        <v>0.99373126046519367</v>
       </c>
       <c r="AP18">
-        <v>184.75912195884121</v>
+        <v>114.92689147144912</v>
       </c>
       <c r="AR18" t="s">
         <v>269</v>
@@ -8010,13 +8010,13 @@
         <v>490</v>
       </c>
       <c r="BB18" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="BC18">
-        <v>0.98987270103949943</v>
+        <v>0.96193435381293269</v>
       </c>
       <c r="BD18">
-        <v>185.6671476091779</v>
+        <v>697.87018009623353</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8081,16 +8081,16 @@
         <v>288</v>
       </c>
       <c r="Y19" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Z19" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="AA19">
-        <v>0.99456953758198319</v>
+        <v>0.99133738566043939</v>
       </c>
       <c r="AB19">
-        <v>99.558477663641582</v>
+        <v>158.81459622527697</v>
       </c>
       <c r="AD19" t="s">
         <v>269</v>
@@ -8120,13 +8120,13 @@
         <v>422</v>
       </c>
       <c r="AN19" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="AO19">
-        <v>0.99027568948244393</v>
+        <v>0.99568755601261638</v>
       </c>
       <c r="AP19">
-        <v>178.27902615519463</v>
+        <v>79.061473102033588</v>
       </c>
       <c r="AR19" t="s">
         <v>269</v>
@@ -8156,13 +8156,13 @@
         <v>491</v>
       </c>
       <c r="BB19" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="BC19">
-        <v>0.98116881440348735</v>
+        <v>0.97296139770869694</v>
       </c>
       <c r="BD19">
-        <v>345.23840260273118</v>
+        <v>495.70770867388939</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8227,16 +8227,16 @@
         <v>290</v>
       </c>
       <c r="Y20" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="Z20" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AA20">
-        <v>0.99082744703600512</v>
+        <v>0.99560473871467581</v>
       </c>
       <c r="AB20">
-        <v>168.16347100657356</v>
+        <v>80.579790230943289</v>
       </c>
       <c r="AD20" t="s">
         <v>269</v>
@@ -8266,13 +8266,13 @@
         <v>423</v>
       </c>
       <c r="AN20" t="s">
-        <v>424</v>
+        <v>335</v>
       </c>
       <c r="AO20">
-        <v>0.98523670671496333</v>
+        <v>0.99099144211961365</v>
       </c>
       <c r="AP20">
-        <v>270.66037689233832</v>
+        <v>165.1568944737499</v>
       </c>
       <c r="AR20" t="s">
         <v>269</v>
@@ -8302,13 +8302,13 @@
         <v>492</v>
       </c>
       <c r="BB20" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="BC20">
-        <v>0.96620291469621566</v>
+        <v>0.97519287309306191</v>
       </c>
       <c r="BD20">
-        <v>619.61323056937977</v>
+        <v>454.79732662719823</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8373,16 +8373,16 @@
         <v>292</v>
       </c>
       <c r="Y21" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="Z21" t="s">
         <v>342</v>
       </c>
       <c r="AA21">
-        <v>0.99238998569866288</v>
+        <v>0.99188284926968906</v>
       </c>
       <c r="AB21">
-        <v>139.51692885784635</v>
+        <v>148.81443005569966</v>
       </c>
       <c r="AD21" t="s">
         <v>269</v>
@@ -8409,16 +8409,16 @@
         <v>375</v>
       </c>
       <c r="AM21" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AN21" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="AO21">
-        <v>0.99104096459785573</v>
+        <v>0.99702764180837389</v>
       </c>
       <c r="AP21">
-        <v>164.24898237264404</v>
+        <v>54.493233513145114</v>
       </c>
       <c r="AR21" t="s">
         <v>269</v>
@@ -8448,13 +8448,13 @@
         <v>493</v>
       </c>
       <c r="BB21" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="BC21">
-        <v>0.96972263277531634</v>
+        <v>0.96620291469621566</v>
       </c>
       <c r="BD21">
-        <v>555.08506578586628</v>
+        <v>619.61323056937977</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8519,16 +8519,16 @@
         <v>294</v>
       </c>
       <c r="Y22" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="Z22" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="AA22">
-        <v>0.99380321394043492</v>
+        <v>0.99628107477919792</v>
       </c>
       <c r="AB22">
-        <v>113.60774442536065</v>
+        <v>68.180295714705792</v>
       </c>
       <c r="AD22" t="s">
         <v>269</v>
@@ -8555,16 +8555,16 @@
         <v>377</v>
       </c>
       <c r="AM22" t="s">
+        <v>425</v>
+      </c>
+      <c r="AN22" t="s">
         <v>426</v>
       </c>
-      <c r="AN22" t="s">
-        <v>427</v>
-      </c>
       <c r="AO22">
-        <v>0.99260627833960313</v>
+        <v>0.98980925931588959</v>
       </c>
       <c r="AP22">
-        <v>135.55156377394354</v>
+        <v>186.83024587535752</v>
       </c>
       <c r="AR22" t="s">
         <v>269</v>
@@ -8594,13 +8594,13 @@
         <v>494</v>
       </c>
       <c r="BB22" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="BC22">
-        <v>0.96193435381293269</v>
+        <v>0.96972263277531634</v>
       </c>
       <c r="BD22">
-        <v>697.87018009623353</v>
+        <v>555.08506578586628</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8665,16 +8665,16 @@
         <v>296</v>
       </c>
       <c r="Y23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Z23" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="AA23">
-        <v>0.98950922221532345</v>
+        <v>0.9922832499015094</v>
       </c>
       <c r="AB23">
-        <v>192.33092605240353</v>
+        <v>141.47375180566112</v>
       </c>
       <c r="AD23" t="s">
         <v>269</v>
@@ -8701,16 +8701,16 @@
         <v>379</v>
       </c>
       <c r="AM23" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AN23" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AO23">
-        <v>0.98220670102649277</v>
+        <v>0.99194279509442385</v>
       </c>
       <c r="AP23">
-        <v>326.21048118096536</v>
+        <v>147.71542326889627</v>
       </c>
       <c r="AR23" t="s">
         <v>269</v>
@@ -8740,13 +8740,13 @@
         <v>495</v>
       </c>
       <c r="BB23" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="BC23">
-        <v>0.97296139770869694</v>
+        <v>0.9861533465577601</v>
       </c>
       <c r="BD23">
-        <v>495.70770867388939</v>
+        <v>253.85531310773223</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8811,16 +8811,16 @@
         <v>298</v>
       </c>
       <c r="Y24" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="Z24" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="AA24">
-        <v>0.99361327661798182</v>
+        <v>0.99427514814587914</v>
       </c>
       <c r="AB24">
-        <v>117.08992867033326</v>
+        <v>104.95561732554863</v>
       </c>
       <c r="AD24" t="s">
         <v>269</v>
@@ -8847,16 +8847,16 @@
         <v>381</v>
       </c>
       <c r="AM24" t="s">
+        <v>428</v>
+      </c>
+      <c r="AN24" t="s">
         <v>429</v>
       </c>
-      <c r="AN24" t="s">
-        <v>430</v>
-      </c>
       <c r="AO24">
-        <v>0.98980925931588959</v>
+        <v>0.9947696749839372</v>
       </c>
       <c r="AP24">
-        <v>186.83024587535752</v>
+        <v>95.889291961151685</v>
       </c>
       <c r="AR24" t="s">
         <v>269</v>
@@ -8886,13 +8886,13 @@
         <v>496</v>
       </c>
       <c r="BB24" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="BC24">
-        <v>0.97519287309306191</v>
+        <v>0.98810453029075374</v>
       </c>
       <c r="BD24">
-        <v>454.79732662719823</v>
+        <v>218.08361133618146</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8957,16 +8957,16 @@
         <v>300</v>
       </c>
       <c r="Y25" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="Z25" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="AA25">
-        <v>0.99105162171633221</v>
+        <v>0.99455764054307205</v>
       </c>
       <c r="AB25">
-        <v>164.05360186724374</v>
+        <v>99.77659004367905</v>
       </c>
       <c r="AD25" t="s">
         <v>269</v>
@@ -8993,16 +8993,16 @@
         <v>383</v>
       </c>
       <c r="AM25" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AN25" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="AO25">
-        <v>0.99194279509442385</v>
+        <v>0.99102447886015177</v>
       </c>
       <c r="AP25">
-        <v>147.71542326889627</v>
+        <v>164.55122089721749</v>
       </c>
       <c r="AR25" t="s">
         <v>269</v>
@@ -9032,7 +9032,7 @@
         <v>497</v>
       </c>
       <c r="BB25" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="BC25">
         <v>0.97260423035674359</v>
@@ -9103,16 +9103,16 @@
         <v>302</v>
       </c>
       <c r="Y26" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="Z26" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AA26">
-        <v>0.99133738566043939</v>
+        <v>0.99510234843435064</v>
       </c>
       <c r="AB26">
-        <v>158.81459622527697</v>
+        <v>89.790278703571531</v>
       </c>
       <c r="AD26" t="s">
         <v>269</v>
@@ -9139,16 +9139,16 @@
         <v>385</v>
       </c>
       <c r="AM26" t="s">
+        <v>431</v>
+      </c>
+      <c r="AN26" t="s">
         <v>432</v>
       </c>
-      <c r="AN26" t="s">
-        <v>427</v>
-      </c>
       <c r="AO26">
-        <v>0.9947696749839372</v>
+        <v>0.99299955705033549</v>
       </c>
       <c r="AP26">
-        <v>95.889291961151685</v>
+        <v>128.34145407718299</v>
       </c>
       <c r="AR26" t="s">
         <v>269</v>
@@ -9178,7 +9178,7 @@
         <v>498</v>
       </c>
       <c r="BB26" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="BC26">
         <v>0.98578667690837229</v>
@@ -9249,16 +9249,16 @@
         <v>304</v>
       </c>
       <c r="Y27" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="Z27" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AA27">
-        <v>0.99560473871467581</v>
+        <v>0.98506785527064555</v>
       </c>
       <c r="AB27">
-        <v>80.579790230943289</v>
+        <v>273.75598670483231</v>
       </c>
       <c r="AD27" t="s">
         <v>269</v>
@@ -9288,13 +9288,13 @@
         <v>433</v>
       </c>
       <c r="AN27" t="s">
-        <v>343</v>
+        <v>429</v>
       </c>
       <c r="AO27">
-        <v>0.99536525245638341</v>
+        <v>0.98967297418060196</v>
       </c>
       <c r="AP27">
-        <v>84.970371632971023</v>
+        <v>189.3288066889647</v>
       </c>
       <c r="AR27" t="s">
         <v>269</v>
@@ -9324,7 +9324,7 @@
         <v>499</v>
       </c>
       <c r="BB27" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="BC27">
         <v>0.98470059323114356</v>
@@ -9395,16 +9395,16 @@
         <v>306</v>
       </c>
       <c r="Y28" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="Z28" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AA28">
-        <v>0.99188284926968906</v>
+        <v>0.99132345360703722</v>
       </c>
       <c r="AB28">
-        <v>148.81443005569966</v>
+        <v>159.07001720431779</v>
       </c>
       <c r="AD28" t="s">
         <v>269</v>
@@ -9434,13 +9434,13 @@
         <v>434</v>
       </c>
       <c r="AN28" t="s">
-        <v>337</v>
+        <v>435</v>
       </c>
       <c r="AO28">
-        <v>0.99668790123920514</v>
+        <v>0.99296607263934833</v>
       </c>
       <c r="AP28">
-        <v>60.721810614572206</v>
+        <v>128.95533494527976</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9505,16 +9505,16 @@
         <v>308</v>
       </c>
       <c r="Y29" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="Z29" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="AA29">
-        <v>0.99628107477919792</v>
+        <v>0.99082744703600512</v>
       </c>
       <c r="AB29">
-        <v>68.180295714705792</v>
+        <v>168.16347100657356</v>
       </c>
       <c r="AD29" t="s">
         <v>269</v>
@@ -9541,16 +9541,16 @@
         <v>391</v>
       </c>
       <c r="AM29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AN29" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AO29">
-        <v>0.99396981584832544</v>
+        <v>0.98992222971133592</v>
       </c>
       <c r="AP29">
-        <v>110.55337611403426</v>
+        <v>184.75912195884121</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9615,16 +9615,16 @@
         <v>310</v>
       </c>
       <c r="Y30" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z30" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="AA30">
-        <v>0.9922832499015094</v>
+        <v>0.99238998569866288</v>
       </c>
       <c r="AB30">
-        <v>141.47375180566112</v>
+        <v>139.51692885784635</v>
       </c>
       <c r="AD30" t="s">
         <v>269</v>
@@ -9651,16 +9651,16 @@
         <v>393</v>
       </c>
       <c r="AM30" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN30" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AO30">
-        <v>0.99102447886015177</v>
+        <v>0.99027568948244393</v>
       </c>
       <c r="AP30">
-        <v>164.55122089721749</v>
+        <v>178.27902615519463</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9725,16 +9725,16 @@
         <v>312</v>
       </c>
       <c r="Y31" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="Z31" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="AA31">
-        <v>0.99427514814587914</v>
+        <v>0.99058732692867291</v>
       </c>
       <c r="AB31">
-        <v>104.95561732554863</v>
+        <v>172.56567297432909</v>
       </c>
       <c r="AD31" t="s">
         <v>269</v>
@@ -9761,16 +9761,16 @@
         <v>395</v>
       </c>
       <c r="AM31" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN31" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO31">
-        <v>0.99299955705033549</v>
+        <v>0.98523670671496333</v>
       </c>
       <c r="AP31">
-        <v>128.34145407718299</v>
+        <v>270.66037689233832</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9835,16 +9835,16 @@
         <v>314</v>
       </c>
       <c r="Y32" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Z32" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AA32">
-        <v>0.98066337855689323</v>
+        <v>0.99456953758198319</v>
       </c>
       <c r="AB32">
-        <v>354.5047264569576</v>
+        <v>99.558477663641582</v>
       </c>
       <c r="AD32" t="s">
         <v>269</v>
@@ -9871,16 +9871,16 @@
         <v>397</v>
       </c>
       <c r="AM32" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN32" t="s">
-        <v>427</v>
+        <v>353</v>
       </c>
       <c r="AO32">
-        <v>0.98967297418060196</v>
+        <v>0.99104096459785573</v>
       </c>
       <c r="AP32">
-        <v>189.3288066889647</v>
+        <v>164.24898237264404</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9945,16 +9945,16 @@
         <v>316</v>
       </c>
       <c r="Y33" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Z33" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA33">
-        <v>0.99010316852626312</v>
+        <v>0.99203796026218938</v>
       </c>
       <c r="AB33">
-        <v>181.44191035184215</v>
+        <v>145.97072852652775</v>
       </c>
       <c r="AD33" t="s">
         <v>269</v>
@@ -9981,16 +9981,16 @@
         <v>399</v>
       </c>
       <c r="AM33" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN33" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="AO33">
-        <v>0.99265977528547111</v>
+        <v>0.99260627833960313</v>
       </c>
       <c r="AP33">
-        <v>134.57078643303035</v>
+        <v>135.55156377394354</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -10055,16 +10055,16 @@
         <v>318</v>
       </c>
       <c r="Y34" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="Z34" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AA34">
-        <v>0.98887858934711803</v>
+        <v>0.99074898552043367</v>
       </c>
       <c r="AB34">
-        <v>203.89252863617014</v>
+        <v>169.6019321253824</v>
       </c>
       <c r="AD34" t="s">
         <v>269</v>
@@ -10094,13 +10094,13 @@
         <v>442</v>
       </c>
       <c r="AN34" t="s">
-        <v>443</v>
+        <v>353</v>
       </c>
       <c r="AO34">
-        <v>0.99102919755488506</v>
+        <v>0.98220670102649277</v>
       </c>
       <c r="AP34">
-        <v>164.46471149377308</v>
+        <v>326.21048118096536</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -10165,16 +10165,16 @@
         <v>320</v>
       </c>
       <c r="Y35" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="Z35" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AA35">
-        <v>0.99455764054307205</v>
+        <v>0.98871903666488603</v>
       </c>
       <c r="AB35">
-        <v>99.77659004367905</v>
+        <v>206.81766114375711</v>
       </c>
       <c r="AD35" t="s">
         <v>269</v>
@@ -10201,16 +10201,16 @@
         <v>403</v>
       </c>
       <c r="AM35" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AN35" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="AO35">
-        <v>0.9782800434603014</v>
+        <v>0.98974092979483974</v>
       </c>
       <c r="AP35">
-        <v>398.19920322780678</v>
+        <v>188.08295376127217</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -10275,16 +10275,16 @@
         <v>322</v>
       </c>
       <c r="Y36" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Z36" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="AA36">
-        <v>0.99510234843435064</v>
+        <v>0.99036558192019719</v>
       </c>
       <c r="AB36">
-        <v>89.790278703571531</v>
+        <v>176.63099812971814</v>
       </c>
       <c r="AD36" t="s">
         <v>269</v>
@@ -10311,16 +10311,16 @@
         <v>405</v>
       </c>
       <c r="AM36" t="s">
+        <v>444</v>
+      </c>
+      <c r="AN36" t="s">
         <v>445</v>
       </c>
-      <c r="AN36" t="s">
-        <v>341</v>
-      </c>
       <c r="AO36">
-        <v>0.99568755601261638</v>
+        <v>0.99454803063103558</v>
       </c>
       <c r="AP36">
-        <v>79.061473102033588</v>
+        <v>99.952771764347304</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -10385,16 +10385,16 @@
         <v>324</v>
       </c>
       <c r="Y37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Z37" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="AA37">
-        <v>0.98506785527064555</v>
+        <v>0.98943698292665661</v>
       </c>
       <c r="AB37">
-        <v>273.75598670483231</v>
+        <v>193.6553130112959</v>
       </c>
       <c r="AD37" t="s">
         <v>269</v>
@@ -10424,13 +10424,13 @@
         <v>446</v>
       </c>
       <c r="AN37" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="AO37">
-        <v>0.99099144211961365</v>
+        <v>0.99668790123920514</v>
       </c>
       <c r="AP37">
-        <v>165.1568944737499</v>
+        <v>60.721810614572206</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10495,16 +10495,16 @@
         <v>326</v>
       </c>
       <c r="Y38" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="Z38" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="AA38">
-        <v>0.99592139175292038</v>
+        <v>0.98844033553992972</v>
       </c>
       <c r="AB38">
-        <v>74.774484529793384</v>
+        <v>211.92718176795447</v>
       </c>
       <c r="AD38" t="s">
         <v>269</v>
@@ -10534,13 +10534,13 @@
         <v>447</v>
       </c>
       <c r="AN38" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="AO38">
-        <v>0.99702764180837389</v>
+        <v>0.99396981584832544</v>
       </c>
       <c r="AP38">
-        <v>54.493233513145114</v>
+        <v>110.55337611403426</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -10605,16 +10605,16 @@
         <v>328</v>
       </c>
       <c r="Y39" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="Z39" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AA39">
-        <v>0.99036558192019719</v>
+        <v>0.97057104063486466</v>
       </c>
       <c r="AB39">
-        <v>176.63099812971814</v>
+        <v>539.53092169414879</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -10679,16 +10679,16 @@
         <v>330</v>
       </c>
       <c r="Y40" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Z40" t="s">
         <v>354</v>
       </c>
       <c r="AA40">
-        <v>0.99203796026218938</v>
+        <v>0.99592139175292038</v>
       </c>
       <c r="AB40">
-        <v>145.97072852652775</v>
+        <v>74.774484529793384</v>
       </c>
     </row>
   </sheetData>
@@ -10697,7 +10697,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43720E71-E287-46FB-9202-0A5FF9046758}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A618D4DB-7A91-4637-8460-520AEED51252}">
   <dimension ref="B9:Z38"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10809,7 +10809,7 @@
         <v>500</v>
       </c>
       <c r="K11" t="s">
-        <v>444</v>
+        <v>415</v>
       </c>
       <c r="L11">
         <v>7.5384385218371168</v>
@@ -10842,7 +10842,7 @@
         <v>556</v>
       </c>
       <c r="X11" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="Y11">
         <v>38.411999999999999</v>
@@ -10877,7 +10877,7 @@
         <v>502</v>
       </c>
       <c r="K12" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="L12">
         <v>8.5464211426904182</v>
@@ -10910,7 +10910,7 @@
         <v>558</v>
       </c>
       <c r="X12" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="Y12">
         <v>9.3112499999999994</v>
@@ -10945,7 +10945,7 @@
         <v>504</v>
       </c>
       <c r="K13" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="L13">
         <v>1.5340845206129941</v>
@@ -10978,7 +10978,7 @@
         <v>560</v>
       </c>
       <c r="X13" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Y13">
         <v>9.5287500000000005</v>
@@ -11013,7 +11013,7 @@
         <v>506</v>
       </c>
       <c r="K14" t="s">
-        <v>447</v>
+        <v>424</v>
       </c>
       <c r="L14">
         <v>17.766367792804527</v>
@@ -11046,7 +11046,7 @@
         <v>562</v>
       </c>
       <c r="X14" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="Y14">
         <v>2.1749999999999999E-2</v>
@@ -11081,7 +11081,7 @@
         <v>508</v>
       </c>
       <c r="K15" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="L15">
         <v>3.7020770759557711</v>
@@ -11114,7 +11114,7 @@
         <v>564</v>
       </c>
       <c r="X15" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Y15">
         <v>8.2590000000000003</v>
@@ -11149,7 +11149,7 @@
         <v>510</v>
       </c>
       <c r="K16" t="s">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="L16">
         <v>28.612118601835597</v>
@@ -11182,7 +11182,7 @@
         <v>566</v>
       </c>
       <c r="X16" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="Y16">
         <v>0.40575</v>
@@ -11217,7 +11217,7 @@
         <v>512</v>
       </c>
       <c r="K17" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="L17">
         <v>54.523871060763341</v>
@@ -11250,7 +11250,7 @@
         <v>568</v>
       </c>
       <c r="X17" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="Y17">
         <v>6.4290000000000003</v>
@@ -11285,7 +11285,7 @@
         <v>514</v>
       </c>
       <c r="K18" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="L18">
         <v>21.752928174024966</v>
@@ -11318,7 +11318,7 @@
         <v>570</v>
       </c>
       <c r="X18" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="Y18">
         <v>0.10199999999999999</v>
@@ -11353,7 +11353,7 @@
         <v>516</v>
       </c>
       <c r="K19" t="s">
-        <v>413</v>
+        <v>443</v>
       </c>
       <c r="L19">
         <v>75.839981284454382</v>
@@ -11421,7 +11421,7 @@
         <v>518</v>
       </c>
       <c r="K20" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="L20">
         <v>15.373849239963436</v>
@@ -11454,7 +11454,7 @@
         <v>574</v>
       </c>
       <c r="X20" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="Y20">
         <v>2.7322500000000001</v>
@@ -11489,7 +11489,7 @@
         <v>520</v>
       </c>
       <c r="K21" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="L21">
         <v>20.941488433116</v>
@@ -11557,7 +11557,7 @@
         <v>522</v>
       </c>
       <c r="K22" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L22">
         <v>10.348692721070078</v>
@@ -11590,7 +11590,7 @@
         <v>578</v>
       </c>
       <c r="X22" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="Y22">
         <v>80.700749999999999</v>
@@ -11625,7 +11625,7 @@
         <v>524</v>
       </c>
       <c r="K23" t="s">
-        <v>445</v>
+        <v>422</v>
       </c>
       <c r="L23">
         <v>30.807418987588004</v>
@@ -11693,7 +11693,7 @@
         <v>526</v>
       </c>
       <c r="K24" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="L24">
         <v>6.8734480919946561</v>
@@ -11726,7 +11726,7 @@
         <v>582</v>
       </c>
       <c r="X24" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="Y24">
         <v>35.221499999999999</v>
@@ -11761,7 +11761,7 @@
         <v>528</v>
       </c>
       <c r="K25" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="L25">
         <v>45.970542554915504</v>
@@ -11829,7 +11829,7 @@
         <v>530</v>
       </c>
       <c r="K26" t="s">
-        <v>440</v>
+        <v>411</v>
       </c>
       <c r="L26">
         <v>102.16105468063856</v>
@@ -11862,7 +11862,7 @@
         <v>586</v>
       </c>
       <c r="X26" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="Y26">
         <v>42.073500000000003</v>
@@ -11897,7 +11897,7 @@
         <v>532</v>
       </c>
       <c r="K27" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L27">
         <v>33.663807794729088</v>
@@ -11930,7 +11930,7 @@
         <v>588</v>
       </c>
       <c r="X27" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="Y27">
         <v>65.507249999999999</v>
@@ -11965,7 +11965,7 @@
         <v>534</v>
       </c>
       <c r="K28" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="L28">
         <v>115.77257062392492</v>
@@ -12000,7 +12000,7 @@
         <v>536</v>
       </c>
       <c r="K29" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="L29">
         <v>18.2196769426582</v>
@@ -12035,7 +12035,7 @@
         <v>538</v>
       </c>
       <c r="K30" t="s">
-        <v>414</v>
+        <v>444</v>
       </c>
       <c r="L30">
         <v>56.340844051935598</v>
@@ -12070,7 +12070,7 @@
         <v>540</v>
       </c>
       <c r="K31" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="L31">
         <v>17.215449395412726</v>
@@ -12105,7 +12105,7 @@
         <v>542</v>
       </c>
       <c r="K32" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="L32">
         <v>30.099997664126345</v>
@@ -12140,7 +12140,7 @@
         <v>544</v>
       </c>
       <c r="K33" t="s">
-        <v>442</v>
+        <v>413</v>
       </c>
       <c r="L33">
         <v>33.688735865274175</v>
@@ -12175,7 +12175,7 @@
         <v>546</v>
       </c>
       <c r="K34" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="L34">
         <v>51.033730360170985</v>
@@ -12210,7 +12210,7 @@
         <v>548</v>
       </c>
       <c r="K35" t="s">
-        <v>446</v>
+        <v>423</v>
       </c>
       <c r="L35">
         <v>96.937146457332247</v>
@@ -12245,7 +12245,7 @@
         <v>550</v>
       </c>
       <c r="K36" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="L36">
         <v>50.741209359452725</v>
@@ -12280,7 +12280,7 @@
         <v>552</v>
       </c>
       <c r="K37" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="L37">
         <v>22.332533209679987</v>
@@ -12315,7 +12315,7 @@
         <v>554</v>
       </c>
       <c r="K38" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="L38">
         <v>43.528633223332768</v>
@@ -12330,7 +12330,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74B9B09D-A947-4333-B8C6-B20E06901124}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9FBD441-95D5-48FA-987D-B76A9787B0A5}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_FRA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E4EAC4B-8D48-49C9-91E8-7941D3F813EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE90203E-449E-431E-9E3C-CB087776DD8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -939,16 +939,118 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_026</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 26</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
   </si>
   <si>
     <t>distr_solelc_spv_014</t>
@@ -963,34 +1065,28 @@
     <t>connecting solar to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_solelc_spv_009</t>
@@ -1029,127 +1125,67 @@
     <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_gen4,e_gen1</t>
+  </si>
+  <si>
     <t>e_dem4,e_gen4</t>
   </si>
   <si>
+    <t>e_gen4</t>
+  </si>
+  <si>
+    <t>e_dem1,e_gen3</t>
+  </si>
+  <si>
+    <t>e_dem2</t>
+  </si>
+  <si>
+    <t>e_gen2</t>
+  </si>
+  <si>
+    <t>e_gen1,e_gen3,e_dem1</t>
+  </si>
+  <si>
+    <t>e_dem0,e_gen2</t>
+  </si>
+  <si>
+    <t>e_gen4,e_dem3</t>
+  </si>
+  <si>
     <t>e_dem0,e_gen3</t>
   </si>
   <si>
+    <t>e_dem4</t>
+  </si>
+  <si>
+    <t>e_dem3</t>
+  </si>
+  <si>
+    <t>e_dem4,e_gen0</t>
+  </si>
+  <si>
+    <t>e_gen2,e_dem0</t>
+  </si>
+  <si>
+    <t>e_dem0,e_gen4,e_gen1</t>
+  </si>
+  <si>
     <t>e_gen1,e_dem1</t>
   </si>
   <si>
-    <t>e_dem2</t>
-  </si>
-  <si>
-    <t>e_gen2</t>
-  </si>
-  <si>
-    <t>e_gen1,e_gen3,e_dem1</t>
-  </si>
-  <si>
-    <t>e_gen4,e_dem3</t>
+    <t>e_dem2,e_gen0,e_gen2</t>
+  </si>
+  <si>
+    <t>e_dem4,e_gen0,e_gen4,e_dem0</t>
+  </si>
+  <si>
+    <t>e_dem3,e_gen1</t>
   </si>
   <si>
     <t>e_gen0,e_dem2</t>
@@ -1158,40 +1194,160 @@
     <t>e_gen0,e_dem2,e_dem0</t>
   </si>
   <si>
-    <t>e_dem4</t>
-  </si>
-  <si>
-    <t>e_gen4,e_gen1</t>
-  </si>
-  <si>
-    <t>e_dem0,e_gen4,e_gen1</t>
-  </si>
-  <si>
-    <t>e_dem4,e_gen0</t>
-  </si>
-  <si>
-    <t>e_dem3,e_gen1</t>
-  </si>
-  <si>
-    <t>e_dem1,e_gen3</t>
-  </si>
-  <si>
-    <t>e_gen4</t>
-  </si>
-  <si>
-    <t>e_gen2,e_dem0</t>
-  </si>
-  <si>
-    <t>e_dem2,e_gen0,e_gen2</t>
-  </si>
-  <si>
-    <t>e_dem4,e_gen0,e_gen4,e_dem0</t>
-  </si>
-  <si>
-    <t>e_dem3</t>
-  </si>
-  <si>
-    <t>e_dem0,e_gen2</t>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
   </si>
   <si>
     <t>distr_wonelc_won_016</t>
@@ -1206,160 +1362,103 @@
     <t>connecting wind onshore to buses in cluster 23</t>
   </si>
   <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_gen3,e_dem1</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_dem2,e_gen2</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_gen1</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_dem1</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_dem2,e_gen0</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_gen4,e_dem0,e_gen1,e_gen3</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_gen0,e_dem4,e_gen4</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
   </si>
   <si>
     <t>elc_won_016</t>
@@ -1374,103 +1473,40 @@
     <t>e_gen1,e_dem1,e_gen3</t>
   </si>
   <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_dem2,e_gen2</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_gen0,e_dem4,e_gen4</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_dem1</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_gen1</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_dem2,e_gen0</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_gen4,e_dem0,e_gen1,e_gen3</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_gen3,e_dem1</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
     <t>distr_wofelc_wof_002</t>
@@ -1491,16 +1527,46 @@
     <t>connecting wind offshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_wofelc_wof_012</t>
@@ -1509,70 +1575,25 @@
     <t>connecting wind offshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_gen0,e_dem2,e_dem4</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
   </si>
   <si>
     <t>elc_wof_002</t>
@@ -1584,49 +1605,28 @@
     <t>elc_wof_008</t>
   </si>
   <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_gen0,e_dem2,e_dem4</t>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
   </si>
   <si>
     <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -6675,7 +6675,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E8D0AD3-E100-47DE-AE76-8D057DD65D98}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87C4697-D30D-4154-888E-C52C55D94E48}">
   <dimension ref="B9:BD40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6913,16 +6913,16 @@
         <v>270</v>
       </c>
       <c r="Y11" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="Z11" t="s">
         <v>334</v>
       </c>
       <c r="AA11">
-        <v>0.99306659504794947</v>
+        <v>0.99036558192019719</v>
       </c>
       <c r="AB11">
-        <v>127.11242412092568</v>
+        <v>176.63099812971814</v>
       </c>
       <c r="AD11" t="s">
         <v>269</v>
@@ -6952,13 +6952,13 @@
         <v>411</v>
       </c>
       <c r="AN11" t="s">
-        <v>412</v>
+        <v>345</v>
       </c>
       <c r="AO11">
-        <v>0.99265977528547111</v>
+        <v>0.9782800434603014</v>
       </c>
       <c r="AP11">
-        <v>134.57078643303035</v>
+        <v>398.19920322780678</v>
       </c>
       <c r="AR11" t="s">
         <v>269</v>
@@ -6988,13 +6988,13 @@
         <v>482</v>
       </c>
       <c r="BB11" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="BC11">
-        <v>0.97024476000465243</v>
+        <v>0.96193435381293269</v>
       </c>
       <c r="BD11">
-        <v>545.51273324803913</v>
+        <v>697.87018009623353</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7059,16 +7059,16 @@
         <v>274</v>
       </c>
       <c r="Y12" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="Z12" t="s">
         <v>335</v>
       </c>
       <c r="AA12">
-        <v>0.99361327661798182</v>
+        <v>0.99306659504794947</v>
       </c>
       <c r="AB12">
-        <v>117.08992867033326</v>
+        <v>127.11242412092568</v>
       </c>
       <c r="AD12" t="s">
         <v>269</v>
@@ -7095,16 +7095,16 @@
         <v>357</v>
       </c>
       <c r="AM12" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AN12" t="s">
-        <v>414</v>
+        <v>336</v>
       </c>
       <c r="AO12">
-        <v>0.99102919755488506</v>
+        <v>0.99568755601261638</v>
       </c>
       <c r="AP12">
-        <v>164.46471149377308</v>
+        <v>79.061473102033588</v>
       </c>
       <c r="AR12" t="s">
         <v>269</v>
@@ -7134,13 +7134,13 @@
         <v>483</v>
       </c>
       <c r="BB12" t="s">
-        <v>418</v>
+        <v>338</v>
       </c>
       <c r="BC12">
-        <v>0.98430504414907682</v>
+        <v>0.97296139770869694</v>
       </c>
       <c r="BD12">
-        <v>287.74085726692596</v>
+        <v>495.70770867388939</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7205,16 +7205,16 @@
         <v>276</v>
       </c>
       <c r="Y13" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="Z13" t="s">
         <v>336</v>
       </c>
       <c r="AA13">
-        <v>0.99105162171633221</v>
+        <v>0.99058732692867291</v>
       </c>
       <c r="AB13">
-        <v>164.05360186724374</v>
+        <v>172.56567297432909</v>
       </c>
       <c r="AD13" t="s">
         <v>269</v>
@@ -7241,16 +7241,16 @@
         <v>359</v>
       </c>
       <c r="AM13" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AN13" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="AO13">
-        <v>0.9782800434603014</v>
+        <v>0.99099144211961365</v>
       </c>
       <c r="AP13">
-        <v>398.19920322780678</v>
+        <v>165.1568944737499</v>
       </c>
       <c r="AR13" t="s">
         <v>269</v>
@@ -7280,13 +7280,13 @@
         <v>484</v>
       </c>
       <c r="BB13" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="BC13">
-        <v>0.99428710319679992</v>
+        <v>0.97519287309306191</v>
       </c>
       <c r="BD13">
-        <v>104.7364413920006</v>
+        <v>454.79732662719823</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7351,16 +7351,16 @@
         <v>278</v>
       </c>
       <c r="Y14" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Z14" t="s">
         <v>337</v>
       </c>
       <c r="AA14">
-        <v>0.98066337855689323</v>
+        <v>0.99456953758198319</v>
       </c>
       <c r="AB14">
-        <v>354.5047264569576</v>
+        <v>99.558477663641582</v>
       </c>
       <c r="AD14" t="s">
         <v>269</v>
@@ -7387,16 +7387,16 @@
         <v>361</v>
       </c>
       <c r="AM14" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AN14" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="AO14">
-        <v>0.99536525245638341</v>
+        <v>0.99702764180837389</v>
       </c>
       <c r="AP14">
-        <v>84.970371632971023</v>
+        <v>54.493233513145114</v>
       </c>
       <c r="AR14" t="s">
         <v>269</v>
@@ -7426,7 +7426,7 @@
         <v>485</v>
       </c>
       <c r="BB14" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="BC14">
         <v>0.98116881440348735</v>
@@ -7497,16 +7497,16 @@
         <v>280</v>
       </c>
       <c r="Y15" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="Z15" t="s">
         <v>338</v>
       </c>
       <c r="AA15">
-        <v>0.99010316852626312</v>
+        <v>0.98066337855689323</v>
       </c>
       <c r="AB15">
-        <v>181.44191035184215</v>
+        <v>354.5047264569576</v>
       </c>
       <c r="AD15" t="s">
         <v>269</v>
@@ -7533,16 +7533,16 @@
         <v>363</v>
       </c>
       <c r="AM15" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AN15" t="s">
-        <v>418</v>
+        <v>335</v>
       </c>
       <c r="AO15">
-        <v>0.98552281783188733</v>
+        <v>0.99102447886015177</v>
       </c>
       <c r="AP15">
-        <v>265.41500641539994</v>
+        <v>164.55122089721749</v>
       </c>
       <c r="AR15" t="s">
         <v>269</v>
@@ -7643,16 +7643,16 @@
         <v>282</v>
       </c>
       <c r="Y16" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="Z16" t="s">
         <v>339</v>
       </c>
       <c r="AA16">
-        <v>0.98887858934711803</v>
+        <v>0.99010316852626312</v>
       </c>
       <c r="AB16">
-        <v>203.89252863617014</v>
+        <v>181.44191035184215</v>
       </c>
       <c r="AD16" t="s">
         <v>269</v>
@@ -7679,16 +7679,16 @@
         <v>365</v>
       </c>
       <c r="AM16" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AN16" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="AO16">
-        <v>0.98584846679356541</v>
+        <v>0.99668790123920514</v>
       </c>
       <c r="AP16">
-        <v>259.44477545130104</v>
+        <v>60.721810614572206</v>
       </c>
       <c r="AR16" t="s">
         <v>269</v>
@@ -7718,13 +7718,13 @@
         <v>488</v>
       </c>
       <c r="BB16" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="BC16">
-        <v>0.98127791933809161</v>
+        <v>0.98470059323114356</v>
       </c>
       <c r="BD16">
-        <v>343.23814546832108</v>
+        <v>280.48912409570232</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7789,16 +7789,16 @@
         <v>284</v>
       </c>
       <c r="Y17" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="Z17" t="s">
         <v>340</v>
       </c>
       <c r="AA17">
-        <v>0.99380321394043492</v>
+        <v>0.98887858934711803</v>
       </c>
       <c r="AB17">
-        <v>113.60774442536065</v>
+        <v>203.89252863617014</v>
       </c>
       <c r="AD17" t="s">
         <v>269</v>
@@ -7825,16 +7825,16 @@
         <v>367</v>
       </c>
       <c r="AM17" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AN17" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AO17">
-        <v>0.99266379654332038</v>
+        <v>0.99396981584832544</v>
       </c>
       <c r="AP17">
-        <v>134.49706337246005</v>
+        <v>110.55337611403426</v>
       </c>
       <c r="AR17" t="s">
         <v>269</v>
@@ -7864,13 +7864,13 @@
         <v>489</v>
       </c>
       <c r="BB17" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="BC17">
-        <v>0.98987270103949943</v>
+        <v>0.97024476000465243</v>
       </c>
       <c r="BD17">
-        <v>185.6671476091779</v>
+        <v>545.51273324803913</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7935,16 +7935,16 @@
         <v>286</v>
       </c>
       <c r="Y18" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="Z18" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="AA18">
-        <v>0.98950922221532345</v>
+        <v>0.99592139175292038</v>
       </c>
       <c r="AB18">
-        <v>192.33092605240353</v>
+        <v>74.774484529793384</v>
       </c>
       <c r="AD18" t="s">
         <v>269</v>
@@ -7971,16 +7971,16 @@
         <v>369</v>
       </c>
       <c r="AM18" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AN18" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="AO18">
-        <v>0.99373126046519367</v>
+        <v>0.98974092979483974</v>
       </c>
       <c r="AP18">
-        <v>114.92689147144912</v>
+        <v>188.08295376127217</v>
       </c>
       <c r="AR18" t="s">
         <v>269</v>
@@ -8010,13 +8010,13 @@
         <v>490</v>
       </c>
       <c r="BB18" t="s">
-        <v>337</v>
+        <v>424</v>
       </c>
       <c r="BC18">
-        <v>0.96193435381293269</v>
+        <v>0.98430504414907682</v>
       </c>
       <c r="BD18">
-        <v>697.87018009623353</v>
+        <v>287.74085726692596</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8081,16 +8081,16 @@
         <v>288</v>
       </c>
       <c r="Y19" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="Z19" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AA19">
-        <v>0.99133738566043939</v>
+        <v>0.99380321394043492</v>
       </c>
       <c r="AB19">
-        <v>158.81459622527697</v>
+        <v>113.60774442536065</v>
       </c>
       <c r="AD19" t="s">
         <v>269</v>
@@ -8117,16 +8117,16 @@
         <v>371</v>
       </c>
       <c r="AM19" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="AN19" t="s">
-        <v>349</v>
+        <v>420</v>
       </c>
       <c r="AO19">
-        <v>0.99568755601261638</v>
+        <v>0.99454803063103558</v>
       </c>
       <c r="AP19">
-        <v>79.061473102033588</v>
+        <v>99.952771764347304</v>
       </c>
       <c r="AR19" t="s">
         <v>269</v>
@@ -8156,13 +8156,13 @@
         <v>491</v>
       </c>
       <c r="BB19" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="BC19">
-        <v>0.97296139770869694</v>
+        <v>0.99428710319679992</v>
       </c>
       <c r="BD19">
-        <v>495.70770867388939</v>
+        <v>104.7364413920006</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8227,16 +8227,16 @@
         <v>290</v>
       </c>
       <c r="Y20" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="Z20" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AA20">
-        <v>0.99560473871467581</v>
+        <v>0.98950922221532345</v>
       </c>
       <c r="AB20">
-        <v>80.579790230943289</v>
+        <v>192.33092605240353</v>
       </c>
       <c r="AD20" t="s">
         <v>269</v>
@@ -8263,16 +8263,16 @@
         <v>373</v>
       </c>
       <c r="AM20" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AN20" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="AO20">
-        <v>0.99099144211961365</v>
+        <v>0.99266379654332038</v>
       </c>
       <c r="AP20">
-        <v>165.1568944737499</v>
+        <v>134.49706337246005</v>
       </c>
       <c r="AR20" t="s">
         <v>269</v>
@@ -8302,13 +8302,13 @@
         <v>492</v>
       </c>
       <c r="BB20" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="BC20">
-        <v>0.97519287309306191</v>
+        <v>0.96620291469621566</v>
       </c>
       <c r="BD20">
-        <v>454.79732662719823</v>
+        <v>619.61323056937977</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8373,16 +8373,16 @@
         <v>292</v>
       </c>
       <c r="Y21" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="Z21" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AA21">
-        <v>0.99188284926968906</v>
+        <v>0.98943698292665661</v>
       </c>
       <c r="AB21">
-        <v>148.81443005569966</v>
+        <v>193.6553130112959</v>
       </c>
       <c r="AD21" t="s">
         <v>269</v>
@@ -8409,16 +8409,16 @@
         <v>375</v>
       </c>
       <c r="AM21" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AN21" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="AO21">
-        <v>0.99702764180837389</v>
+        <v>0.99373126046519367</v>
       </c>
       <c r="AP21">
-        <v>54.493233513145114</v>
+        <v>114.92689147144912</v>
       </c>
       <c r="AR21" t="s">
         <v>269</v>
@@ -8448,13 +8448,13 @@
         <v>493</v>
       </c>
       <c r="BB21" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="BC21">
-        <v>0.96620291469621566</v>
+        <v>0.96972263277531634</v>
       </c>
       <c r="BD21">
-        <v>619.61323056937977</v>
+        <v>555.08506578586628</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8519,16 +8519,16 @@
         <v>294</v>
       </c>
       <c r="Y22" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="Z22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AA22">
-        <v>0.99628107477919792</v>
+        <v>0.98844033553992972</v>
       </c>
       <c r="AB22">
-        <v>68.180295714705792</v>
+        <v>211.92718176795447</v>
       </c>
       <c r="AD22" t="s">
         <v>269</v>
@@ -8555,16 +8555,16 @@
         <v>377</v>
       </c>
       <c r="AM22" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AN22" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AO22">
-        <v>0.98980925931588959</v>
+        <v>0.98552281783188733</v>
       </c>
       <c r="AP22">
-        <v>186.83024587535752</v>
+        <v>265.41500641539994</v>
       </c>
       <c r="AR22" t="s">
         <v>269</v>
@@ -8594,13 +8594,13 @@
         <v>494</v>
       </c>
       <c r="BB22" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="BC22">
-        <v>0.96972263277531634</v>
+        <v>0.98987270103949943</v>
       </c>
       <c r="BD22">
-        <v>555.08506578586628</v>
+        <v>185.6671476091779</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8665,16 +8665,16 @@
         <v>296</v>
       </c>
       <c r="Y23" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="Z23" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="AA23">
-        <v>0.9922832499015094</v>
+        <v>0.97057104063486466</v>
       </c>
       <c r="AB23">
-        <v>141.47375180566112</v>
+        <v>539.53092169414879</v>
       </c>
       <c r="AD23" t="s">
         <v>269</v>
@@ -8701,16 +8701,16 @@
         <v>379</v>
       </c>
       <c r="AM23" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AN23" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="AO23">
-        <v>0.99194279509442385</v>
+        <v>0.98584846679356541</v>
       </c>
       <c r="AP23">
-        <v>147.71542326889627</v>
+        <v>259.44477545130104</v>
       </c>
       <c r="AR23" t="s">
         <v>269</v>
@@ -8740,13 +8740,13 @@
         <v>495</v>
       </c>
       <c r="BB23" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="BC23">
-        <v>0.9861533465577601</v>
+        <v>0.97260423035674359</v>
       </c>
       <c r="BD23">
-        <v>253.85531310773223</v>
+        <v>502.2557767930341</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8811,16 +8811,16 @@
         <v>298</v>
       </c>
       <c r="Y24" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="Z24" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AA24">
-        <v>0.99427514814587914</v>
+        <v>0.99132345360703722</v>
       </c>
       <c r="AB24">
-        <v>104.95561732554863</v>
+        <v>159.07001720431779</v>
       </c>
       <c r="AD24" t="s">
         <v>269</v>
@@ -8847,16 +8847,16 @@
         <v>381</v>
       </c>
       <c r="AM24" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AN24" t="s">
-        <v>429</v>
+        <v>352</v>
       </c>
       <c r="AO24">
-        <v>0.9947696749839372</v>
+        <v>0.99536525245638341</v>
       </c>
       <c r="AP24">
-        <v>95.889291961151685</v>
+        <v>84.970371632971023</v>
       </c>
       <c r="AR24" t="s">
         <v>269</v>
@@ -8886,13 +8886,13 @@
         <v>496</v>
       </c>
       <c r="BB24" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="BC24">
-        <v>0.98810453029075374</v>
+        <v>0.98578667690837229</v>
       </c>
       <c r="BD24">
-        <v>218.08361133618146</v>
+        <v>260.57759001317498</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8957,16 +8957,16 @@
         <v>300</v>
       </c>
       <c r="Y25" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="Z25" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="AA25">
-        <v>0.99455764054307205</v>
+        <v>0.99203796026218938</v>
       </c>
       <c r="AB25">
-        <v>99.77659004367905</v>
+        <v>145.97072852652775</v>
       </c>
       <c r="AD25" t="s">
         <v>269</v>
@@ -8993,16 +8993,16 @@
         <v>383</v>
       </c>
       <c r="AM25" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="AN25" t="s">
-        <v>334</v>
+        <v>428</v>
       </c>
       <c r="AO25">
-        <v>0.99102447886015177</v>
+        <v>0.99299955705033549</v>
       </c>
       <c r="AP25">
-        <v>164.55122089721749</v>
+        <v>128.34145407718299</v>
       </c>
       <c r="AR25" t="s">
         <v>269</v>
@@ -9032,13 +9032,13 @@
         <v>497</v>
       </c>
       <c r="BB25" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="BC25">
-        <v>0.97260423035674359</v>
+        <v>0.9861533465577601</v>
       </c>
       <c r="BD25">
-        <v>502.2557767930341</v>
+        <v>253.85531310773223</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9103,16 +9103,16 @@
         <v>302</v>
       </c>
       <c r="Y26" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="Z26" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="AA26">
-        <v>0.99510234843435064</v>
+        <v>0.99455764054307205</v>
       </c>
       <c r="AB26">
-        <v>89.790278703571531</v>
+        <v>99.77659004367905</v>
       </c>
       <c r="AD26" t="s">
         <v>269</v>
@@ -9139,16 +9139,16 @@
         <v>385</v>
       </c>
       <c r="AM26" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AN26" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AO26">
-        <v>0.99299955705033549</v>
+        <v>0.98967297418060196</v>
       </c>
       <c r="AP26">
-        <v>128.34145407718299</v>
+        <v>189.3288066889647</v>
       </c>
       <c r="AR26" t="s">
         <v>269</v>
@@ -9178,13 +9178,13 @@
         <v>498</v>
       </c>
       <c r="BB26" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC26">
-        <v>0.98578667690837229</v>
+        <v>0.98810453029075374</v>
       </c>
       <c r="BD26">
-        <v>260.57759001317498</v>
+        <v>218.08361133618146</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9249,16 +9249,16 @@
         <v>304</v>
       </c>
       <c r="Y27" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Z27" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="AA27">
-        <v>0.98506785527064555</v>
+        <v>0.99510234843435064</v>
       </c>
       <c r="AB27">
-        <v>273.75598670483231</v>
+        <v>89.790278703571531</v>
       </c>
       <c r="AD27" t="s">
         <v>269</v>
@@ -9285,16 +9285,16 @@
         <v>387</v>
       </c>
       <c r="AM27" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AN27" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AO27">
-        <v>0.98967297418060196</v>
+        <v>0.99296607263934833</v>
       </c>
       <c r="AP27">
-        <v>189.3288066889647</v>
+        <v>128.95533494527976</v>
       </c>
       <c r="AR27" t="s">
         <v>269</v>
@@ -9324,13 +9324,13 @@
         <v>499</v>
       </c>
       <c r="BB27" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="BC27">
-        <v>0.98470059323114356</v>
+        <v>0.98127791933809161</v>
       </c>
       <c r="BD27">
-        <v>280.48912409570232</v>
+        <v>343.23814546832108</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9395,16 +9395,16 @@
         <v>306</v>
       </c>
       <c r="Y28" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="Z28" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AA28">
-        <v>0.99132345360703722</v>
+        <v>0.98506785527064555</v>
       </c>
       <c r="AB28">
-        <v>159.07001720431779</v>
+        <v>273.75598670483231</v>
       </c>
       <c r="AD28" t="s">
         <v>269</v>
@@ -9431,16 +9431,16 @@
         <v>389</v>
       </c>
       <c r="AM28" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AN28" t="s">
-        <v>435</v>
+        <v>335</v>
       </c>
       <c r="AO28">
-        <v>0.99296607263934833</v>
+        <v>0.98992222971133592</v>
       </c>
       <c r="AP28">
-        <v>128.95533494527976</v>
+        <v>184.75912195884121</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9505,16 +9505,16 @@
         <v>308</v>
       </c>
       <c r="Y29" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="Z29" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="AA29">
-        <v>0.99082744703600512</v>
+        <v>0.99361327661798182</v>
       </c>
       <c r="AB29">
-        <v>168.16347100657356</v>
+        <v>117.08992867033326</v>
       </c>
       <c r="AD29" t="s">
         <v>269</v>
@@ -9541,16 +9541,16 @@
         <v>391</v>
       </c>
       <c r="AM29" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AN29" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="AO29">
-        <v>0.98992222971133592</v>
+        <v>0.99027568948244393</v>
       </c>
       <c r="AP29">
-        <v>184.75912195884121</v>
+        <v>178.27902615519463</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9615,16 +9615,16 @@
         <v>310</v>
       </c>
       <c r="Y30" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="Z30" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA30">
-        <v>0.99238998569866288</v>
+        <v>0.99105162171633221</v>
       </c>
       <c r="AB30">
-        <v>139.51692885784635</v>
+        <v>164.05360186724374</v>
       </c>
       <c r="AD30" t="s">
         <v>269</v>
@@ -9651,16 +9651,16 @@
         <v>393</v>
       </c>
       <c r="AM30" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AN30" t="s">
-        <v>340</v>
+        <v>436</v>
       </c>
       <c r="AO30">
-        <v>0.99027568948244393</v>
+        <v>0.98523670671496333</v>
       </c>
       <c r="AP30">
-        <v>178.27902615519463</v>
+        <v>270.66037689233832</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9725,16 +9725,16 @@
         <v>312</v>
       </c>
       <c r="Y31" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="Z31" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA31">
-        <v>0.99058732692867291</v>
+        <v>0.99074898552043367</v>
       </c>
       <c r="AB31">
-        <v>172.56567297432909</v>
+        <v>169.6019321253824</v>
       </c>
       <c r="AD31" t="s">
         <v>269</v>
@@ -9761,16 +9761,16 @@
         <v>395</v>
       </c>
       <c r="AM31" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AN31" t="s">
-        <v>439</v>
+        <v>345</v>
       </c>
       <c r="AO31">
-        <v>0.98523670671496333</v>
+        <v>0.99104096459785573</v>
       </c>
       <c r="AP31">
-        <v>270.66037689233832</v>
+        <v>164.24898237264404</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9835,16 +9835,16 @@
         <v>314</v>
       </c>
       <c r="Y32" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="Z32" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AA32">
-        <v>0.99456953758198319</v>
+        <v>0.98871903666488603</v>
       </c>
       <c r="AB32">
-        <v>99.558477663641582</v>
+        <v>206.81766114375711</v>
       </c>
       <c r="AD32" t="s">
         <v>269</v>
@@ -9871,16 +9871,16 @@
         <v>397</v>
       </c>
       <c r="AM32" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AN32" t="s">
-        <v>353</v>
+        <v>430</v>
       </c>
       <c r="AO32">
-        <v>0.99104096459785573</v>
+        <v>0.99260627833960313</v>
       </c>
       <c r="AP32">
-        <v>164.24898237264404</v>
+        <v>135.55156377394354</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9945,16 +9945,16 @@
         <v>316</v>
       </c>
       <c r="Y33" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="Z33" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AA33">
-        <v>0.99203796026218938</v>
+        <v>0.99082744703600512</v>
       </c>
       <c r="AB33">
-        <v>145.97072852652775</v>
+        <v>168.16347100657356</v>
       </c>
       <c r="AD33" t="s">
         <v>269</v>
@@ -9981,16 +9981,16 @@
         <v>399</v>
       </c>
       <c r="AM33" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AN33" t="s">
-        <v>429</v>
+        <v>345</v>
       </c>
       <c r="AO33">
-        <v>0.99260627833960313</v>
+        <v>0.98220670102649277</v>
       </c>
       <c r="AP33">
-        <v>135.55156377394354</v>
+        <v>326.21048118096536</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -10055,16 +10055,16 @@
         <v>318</v>
       </c>
       <c r="Y34" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Z34" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="AA34">
-        <v>0.99074898552043367</v>
+        <v>0.99238998569866288</v>
       </c>
       <c r="AB34">
-        <v>169.6019321253824</v>
+        <v>139.51692885784635</v>
       </c>
       <c r="AD34" t="s">
         <v>269</v>
@@ -10091,16 +10091,16 @@
         <v>401</v>
       </c>
       <c r="AM34" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AN34" t="s">
-        <v>353</v>
+        <v>441</v>
       </c>
       <c r="AO34">
-        <v>0.98220670102649277</v>
+        <v>0.98980925931588959</v>
       </c>
       <c r="AP34">
-        <v>326.21048118096536</v>
+        <v>186.83024587535752</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -10165,16 +10165,16 @@
         <v>320</v>
       </c>
       <c r="Y35" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="Z35" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="AA35">
-        <v>0.98871903666488603</v>
+        <v>0.99133738566043939</v>
       </c>
       <c r="AB35">
-        <v>206.81766114375711</v>
+        <v>158.81459622527697</v>
       </c>
       <c r="AD35" t="s">
         <v>269</v>
@@ -10201,16 +10201,16 @@
         <v>403</v>
       </c>
       <c r="AM35" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AN35" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AO35">
-        <v>0.98974092979483974</v>
+        <v>0.99194279509442385</v>
       </c>
       <c r="AP35">
-        <v>188.08295376127217</v>
+        <v>147.71542326889627</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -10275,16 +10275,16 @@
         <v>322</v>
       </c>
       <c r="Y36" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="Z36" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="AA36">
-        <v>0.99036558192019719</v>
+        <v>0.99560473871467581</v>
       </c>
       <c r="AB36">
-        <v>176.63099812971814</v>
+        <v>80.579790230943289</v>
       </c>
       <c r="AD36" t="s">
         <v>269</v>
@@ -10311,16 +10311,16 @@
         <v>405</v>
       </c>
       <c r="AM36" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AN36" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="AO36">
-        <v>0.99454803063103558</v>
+        <v>0.9947696749839372</v>
       </c>
       <c r="AP36">
-        <v>99.952771764347304</v>
+        <v>95.889291961151685</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -10385,16 +10385,16 @@
         <v>324</v>
       </c>
       <c r="Y37" t="s">
-        <v>262</v>
+        <v>243</v>
       </c>
       <c r="Z37" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="AA37">
-        <v>0.98943698292665661</v>
+        <v>0.99188284926968906</v>
       </c>
       <c r="AB37">
-        <v>193.6553130112959</v>
+        <v>148.81443005569966</v>
       </c>
       <c r="AD37" t="s">
         <v>269</v>
@@ -10421,16 +10421,16 @@
         <v>407</v>
       </c>
       <c r="AM37" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AN37" t="s">
-        <v>334</v>
+        <v>445</v>
       </c>
       <c r="AO37">
-        <v>0.99668790123920514</v>
+        <v>0.99265977528547111</v>
       </c>
       <c r="AP37">
-        <v>60.721810614572206</v>
+        <v>134.57078643303035</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10495,16 +10495,16 @@
         <v>326</v>
       </c>
       <c r="Y38" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="Z38" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AA38">
-        <v>0.98844033553992972</v>
+        <v>0.99628107477919792</v>
       </c>
       <c r="AB38">
-        <v>211.92718176795447</v>
+        <v>68.180295714705792</v>
       </c>
       <c r="AD38" t="s">
         <v>269</v>
@@ -10531,16 +10531,16 @@
         <v>409</v>
       </c>
       <c r="AM38" t="s">
+        <v>446</v>
+      </c>
+      <c r="AN38" t="s">
         <v>447</v>
       </c>
-      <c r="AN38" t="s">
-        <v>353</v>
-      </c>
       <c r="AO38">
-        <v>0.99396981584832544</v>
+        <v>0.99102919755488506</v>
       </c>
       <c r="AP38">
-        <v>110.55337611403426</v>
+        <v>164.46471149377308</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -10605,16 +10605,16 @@
         <v>328</v>
       </c>
       <c r="Y39" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="Z39" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="AA39">
-        <v>0.97057104063486466</v>
+        <v>0.9922832499015094</v>
       </c>
       <c r="AB39">
-        <v>539.53092169414879</v>
+        <v>141.47375180566112</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -10679,16 +10679,16 @@
         <v>330</v>
       </c>
       <c r="Y40" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="Z40" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="AA40">
-        <v>0.99592139175292038</v>
+        <v>0.99427514814587914</v>
       </c>
       <c r="AB40">
-        <v>74.774484529793384</v>
+        <v>104.95561732554863</v>
       </c>
     </row>
   </sheetData>
@@ -10697,7 +10697,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A618D4DB-7A91-4637-8460-520AEED51252}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BCD021F-0F73-44B7-B305-BBDFF94C9379}">
   <dimension ref="B9:Z38"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10809,7 +10809,7 @@
         <v>500</v>
       </c>
       <c r="K11" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="L11">
         <v>7.5384385218371168</v>
@@ -10842,7 +10842,7 @@
         <v>556</v>
       </c>
       <c r="X11" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="Y11">
         <v>38.411999999999999</v>
@@ -10877,7 +10877,7 @@
         <v>502</v>
       </c>
       <c r="K12" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="L12">
         <v>8.5464211426904182</v>
@@ -10910,7 +10910,7 @@
         <v>558</v>
       </c>
       <c r="X12" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="Y12">
         <v>9.3112499999999994</v>
@@ -10945,7 +10945,7 @@
         <v>504</v>
       </c>
       <c r="K13" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="L13">
         <v>1.5340845206129941</v>
@@ -10978,7 +10978,7 @@
         <v>560</v>
       </c>
       <c r="X13" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="Y13">
         <v>9.5287500000000005</v>
@@ -11013,7 +11013,7 @@
         <v>506</v>
       </c>
       <c r="K14" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="L14">
         <v>17.766367792804527</v>
@@ -11081,7 +11081,7 @@
         <v>508</v>
       </c>
       <c r="K15" t="s">
-        <v>447</v>
+        <v>417</v>
       </c>
       <c r="L15">
         <v>3.7020770759557711</v>
@@ -11114,7 +11114,7 @@
         <v>564</v>
       </c>
       <c r="X15" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="Y15">
         <v>8.2590000000000003</v>
@@ -11149,7 +11149,7 @@
         <v>510</v>
       </c>
       <c r="K16" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="L16">
         <v>28.612118601835597</v>
@@ -11182,7 +11182,7 @@
         <v>566</v>
       </c>
       <c r="X16" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="Y16">
         <v>0.40575</v>
@@ -11217,7 +11217,7 @@
         <v>512</v>
       </c>
       <c r="K17" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="L17">
         <v>54.523871060763341</v>
@@ -11250,7 +11250,7 @@
         <v>568</v>
       </c>
       <c r="X17" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="Y17">
         <v>6.4290000000000003</v>
@@ -11285,7 +11285,7 @@
         <v>514</v>
       </c>
       <c r="K18" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="L18">
         <v>21.752928174024966</v>
@@ -11318,7 +11318,7 @@
         <v>570</v>
       </c>
       <c r="X18" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="Y18">
         <v>0.10199999999999999</v>
@@ -11353,7 +11353,7 @@
         <v>516</v>
       </c>
       <c r="K19" t="s">
-        <v>443</v>
+        <v>418</v>
       </c>
       <c r="L19">
         <v>75.839981284454382</v>
@@ -11386,7 +11386,7 @@
         <v>572</v>
       </c>
       <c r="X19" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="Y19">
         <v>27.910499999999999</v>
@@ -11421,7 +11421,7 @@
         <v>518</v>
       </c>
       <c r="K20" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L20">
         <v>15.373849239963436</v>
@@ -11454,7 +11454,7 @@
         <v>574</v>
       </c>
       <c r="X20" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="Y20">
         <v>2.7322500000000001</v>
@@ -11489,7 +11489,7 @@
         <v>520</v>
       </c>
       <c r="K21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L21">
         <v>20.941488433116</v>
@@ -11557,7 +11557,7 @@
         <v>522</v>
       </c>
       <c r="K22" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="L22">
         <v>10.348692721070078</v>
@@ -11590,7 +11590,7 @@
         <v>578</v>
       </c>
       <c r="X22" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="Y22">
         <v>80.700749999999999</v>
@@ -11625,7 +11625,7 @@
         <v>524</v>
       </c>
       <c r="K23" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="L23">
         <v>30.807418987588004</v>
@@ -11658,7 +11658,7 @@
         <v>580</v>
       </c>
       <c r="X23" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="Y23">
         <v>19.849499999999999</v>
@@ -11693,7 +11693,7 @@
         <v>526</v>
       </c>
       <c r="K24" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="L24">
         <v>6.8734480919946561</v>
@@ -11726,7 +11726,7 @@
         <v>582</v>
       </c>
       <c r="X24" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="Y24">
         <v>35.221499999999999</v>
@@ -11761,7 +11761,7 @@
         <v>528</v>
       </c>
       <c r="K25" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="L25">
         <v>45.970542554915504</v>
@@ -11794,7 +11794,7 @@
         <v>584</v>
       </c>
       <c r="X25" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="Y25">
         <v>88.549499999999995</v>
@@ -11829,7 +11829,7 @@
         <v>530</v>
       </c>
       <c r="K26" t="s">
-        <v>411</v>
+        <v>444</v>
       </c>
       <c r="L26">
         <v>102.16105468063856</v>
@@ -11862,7 +11862,7 @@
         <v>586</v>
       </c>
       <c r="X26" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="Y26">
         <v>42.073500000000003</v>
@@ -11897,7 +11897,7 @@
         <v>532</v>
       </c>
       <c r="K27" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="L27">
         <v>33.663807794729088</v>
@@ -11930,7 +11930,7 @@
         <v>588</v>
       </c>
       <c r="X27" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="Y27">
         <v>65.507249999999999</v>
@@ -11965,7 +11965,7 @@
         <v>534</v>
       </c>
       <c r="K28" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="L28">
         <v>115.77257062392492</v>
@@ -12000,7 +12000,7 @@
         <v>536</v>
       </c>
       <c r="K29" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="L29">
         <v>18.2196769426582</v>
@@ -12035,7 +12035,7 @@
         <v>538</v>
       </c>
       <c r="K30" t="s">
-        <v>444</v>
+        <v>419</v>
       </c>
       <c r="L30">
         <v>56.340844051935598</v>
@@ -12070,7 +12070,7 @@
         <v>540</v>
       </c>
       <c r="K31" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="L31">
         <v>17.215449395412726</v>
@@ -12105,7 +12105,7 @@
         <v>542</v>
       </c>
       <c r="K32" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="L32">
         <v>30.099997664126345</v>
@@ -12140,7 +12140,7 @@
         <v>544</v>
       </c>
       <c r="K33" t="s">
-        <v>413</v>
+        <v>446</v>
       </c>
       <c r="L33">
         <v>33.688735865274175</v>
@@ -12175,7 +12175,7 @@
         <v>546</v>
       </c>
       <c r="K34" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="L34">
         <v>51.033730360170985</v>
@@ -12210,7 +12210,7 @@
         <v>548</v>
       </c>
       <c r="K35" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="L35">
         <v>96.937146457332247</v>
@@ -12245,7 +12245,7 @@
         <v>550</v>
       </c>
       <c r="K36" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="L36">
         <v>50.741209359452725</v>
@@ -12280,7 +12280,7 @@
         <v>552</v>
       </c>
       <c r="K37" t="s">
-        <v>446</v>
+        <v>416</v>
       </c>
       <c r="L37">
         <v>22.332533209679987</v>
@@ -12315,7 +12315,7 @@
         <v>554</v>
       </c>
       <c r="K38" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="L38">
         <v>43.528633223332768</v>
@@ -12330,7 +12330,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9FBD441-95D5-48FA-987D-B76A9787B0A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED632598-1F47-4695-8125-AA8DF05A6B5B}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
